--- a/valuega/밸루가_QA검증요청_회신초안_20260812.xlsx
+++ b/valuega/밸루가_QA검증요청_회신초안_20260812.xlsx
@@ -10,8 +10,10 @@
     <sheet name="1_요청사항요약" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2_QA건별회신" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3_답변어투가이드" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4_모범답변예시" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5_데이터확인필요_회신" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3-1_프롬프트문구초안" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3-2_어투검수체크리스트" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4_모범답변예시" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5_데이터확인필요_회신" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_QA건별회신'!$A$1:$J$16</definedName>
@@ -23,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +65,22 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -137,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,16 +186,21 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -615,8 +638,11 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>· [3_답변어투가이드] 시트 전달 (금지표현 → 대체표현 + 답변 구조 템플릿)
-· [4_모범답변예시] 시트의 기대답변 16건을 톤 레퍼런스로 함께 전달</t>
+          <t>· [3_답변어투가이드] 금지표현 사전(21개) + 답변 구조 템플릿 + Before/After 6건
+· [3-1_프롬프트문구초안] 그대로 반영 가능한 프롬프트 블록 11개 규칙
+· [3-2_어투검수체크리스트] 반영 후 재검증용 (키워드 자동 검출 가능)
+· [4_모범답변예시] 기대답변 16건을 톤 레퍼런스로 함께 전달
+※ 실측: 밸루가 분류 4건이 아니라 답변 생성 9건 전부에서 발생 중</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1061,8 +1087,9 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>요청하신 톤·문장 예시를 [3_답변어투가이드] 시트로 전달드립니다.
-· 금지표현 → 대체표현 매핑표, 답변 구조 템플릿, Before/After 예시 포함
+          <t>요청하신 톤·문장 예시를 [3_답변어투가이드] / [3-1_프롬프트문구초안] 시트로 전달드립니다.
+· 금지표현 사전(21개), 답변 구조 템플릿, Before/After 6건 포함
+· [3-1] 블록은 시스템 프롬프트에 그대로 반영 가능한 형태로 작성했습니다.
 · 추가로 [4_모범답변예시] 시트의 기대답변 16건을 실제 톤 레퍼런스로 활용해 주시기 바랍니다.
 · 유지 요청: 학습 내용을 찾지 못한 경우의 기존 fallback 안내 문구는 현행 유지가 맞습니다.</t>
         </is>
@@ -1318,8 +1345,8 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>[3_답변어투가이드] 시트로 톤·예시 문장 전달드립니다.
-· 해당 건 Before/After 예시를 가이드에 포함했습니다.
+          <t>[3_답변어투가이드] / [3-1_프롬프트문구초안] 시트로 톤·예시 문장 전달드립니다.
+· 해당 건 Before/After 예시를 가이드에 포함했습니다. (출처 언급 9회 발생)
 · 핵심: 출처 언급 서두(제공된 자료/학습된 내용) 전면 삭제 후 두괄식 결론으로 시작.</t>
         </is>
       </c>
@@ -1368,7 +1395,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>[3_답변어투가이드] 시트로 톤·예시 문장 전달드립니다.
+          <t>[3_답변어투가이드] / [3-1_프롬프트문구초안] 시트로 톤·예시 문장 전달드립니다. (해당 건 Before/After 포함)
 · 추가 요청: 본문에서 이미 답변(100세 만기)을 제공했음에도 말미에 "현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다" fallback 문구가 중복 출력되고 있습니다. 답변이 생성된 경우 fallback이 함께 붙지 않도록 분기 처리 부탁드립니다. (No.16도 동일 현상)</t>
         </is>
       </c>
@@ -1417,8 +1444,8 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>[3_답변어투가이드] 시트로 톤·예시 문장 전달드립니다.
-· 해당 건 Before/After 예시를 가이드에 포함했습니다.</t>
+          <t>[3_답변어투가이드] / [3-1_프롬프트문구초안] 시트로 톤·예시 문장 전달드립니다.
+· 해당 건 Before/After 예시를 가이드에 포함했습니다. (출처 언급 10회 발생)</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1596,13 +1623,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1615,704 +1642,1158 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>적용 대상: FA AI / Orca AI 공통 · 관련 QA 건: No.6, 8, 11, 12, 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
+          <t>적용 대상: FA AI / Orca AI 공통 · 해당 QA 건: 답변이 생성된 9건 전부 (No.3, 4, 6, 8, 10, 11, 12, 13, 16) — 밸루가 "프롬프트 개선" 분류는 4건이나 실제 발생은 9건</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="67.5" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>원칙 1. 답변은 "고객에게 말하는 문장"이다 — 검색 결과 보고서가 아니다</t>
+          <t>현황. 출처 언급 어투는 "프롬프트 개선" 분류 4건이 아니라, 답변이 생성된 9건 전부에서 발생 중</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
     </row>
-    <row r="4" ht="42" customHeight="1">
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
         <is>
+          <t>QA 번호</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>출처 언급 횟수</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>주요 출현 표현</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>밸루가 분류</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="27" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>No.10 통풍환자 가입가능 보험</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>19회</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>되어 있습니다(7) · 제공된 자료(2) · 안내되어 있습니다(2) · 자료상 · 자료에 명시 · 자료에 등장</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="27" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>No.3 다이렉트 보험 가입</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>11회</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>자료에 따르면(4) · 제공된 자료(2) · 되어 있습니다(2) · 자료 기준(2)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>No.12 실비보험 만기</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>10회</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>제공된 자료(3) · 근거가 부족 · 정리되어 있습니다 · 자료상</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>프롬프트 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>No.13 고양이 펫보험</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>10회</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>되어 있습니다(2) · 자료에는(2) · 확인됩니다 · 안내되어 있습니다</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>프롬프트 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>No.11 실비 단독설계</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>9회</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>되어 있습니다(4) · 제공된 자료(2) · 안내되어 있습니다(2) · 정리되어 있습니다</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>프롬프트 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>No.16 퀵 가입설계 비교</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>7회</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>제공된 자료(2) · 제공 자료 · 자료 기준 · 자료에는</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>No.4 화상 진단비</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2회</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>제공된 약관 · 자료에는</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>(미분류)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>No.6 클레임 대응</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1회</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>제공된 내용의 관점에서는</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>프롬프트 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>No.8 명함 제작</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1회</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>질의응답 기준으로는</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>데이터확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="94.5" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>[참고] No.2 · No.14 · No.15는 "학습된 내용" 문구가 있으나 답변 미생성 시의 fallback 안내문이므로 정상입니다. 현행 유지가 맞습니다.</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>원칙 1. 답변은 "고객에게 말하는 문장"이다 — 검색 결과 보고서가 아니다</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>원칙</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="17" ht="27" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>출처 언급 서두를 쓰지 않는다</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>"제공된 자료 기준으로는", "학습한 자료에 따르면", "자료에 따르면", "제공된 약관 내용에는" 등은 문장에서 통째로 삭제하고 바로 본론으로 들어간다.</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>가장 다수 지적 사항</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>전언체(~라고 되어 있습니다)를 단정체(~입니다)로 바꾼다</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>지식 출처가 사내 문서라는 사실은 시스템 내부 사정이므로 문장에 드러내지 않는다.</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>두괄식으로 시작한다</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>"결론부터 말씀드리면, ~" 형태로 첫 문장에 답을 준다. 배경 설명은 그 뒤.</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>모르는 것은 "근거 부족"이 아니라 "확인이 필요한 항목"으로 표현한다</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>"확정할 근거가 부족합니다"(X) → "정확히 안내드리려면 가입하신 상품명 확인이 필요합니다"(O)</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>1-5</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>근거 문서에 상품명·기관명이 있으면 반드시 특정해서 말한다</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>"어떤 자료에 있습니다"로 끝내지 말고 상품명/팀명/연락처까지 명시한다.</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>QA No.10 관련</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>1-6</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>없는 내용을 추론해서 단정하지 않는다</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>원문에 없는 제약("임의 제작은 불가")을 만들어내지 않는다. 원문 범위 내에서만 단정한다.</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>QA No.8 관련</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="23" ht="27" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>1-7</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>답변이 생성된 경우 fallback 문구를 함께 붙이지 않는다</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>본문 답변이 있는데 말미에 "현재 학습된 내용에는 ~ 어렵습니다"가 중복 출력되지 않도록 분기한다.</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>QA No.12, 16 관련</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>1-8</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>학습 내용이 전혀 없을 때의 기존 fallback 문구는 그대로 유지한다</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>"현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다 ~" 안내는 현행 유지가 맞다.</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>유지 요청</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>원칙 2. 금지 표현 → 대체 표현 매핑표</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="25" ht="67.5" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>원칙 2. 금지 표현 → 대체 표현 사전 (A: 출처 언급 / B: 전언체 / C: 시스템 한계 노출)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>금지 표현 (현재 출력)</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>대체 표현 (권장)</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>적용 예</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>제공된 자료 기준으로는 ~입니다</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>(삭제) ~입니다</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>"제공된 자료 기준으로는 다이렉트 보험은 ~" → "다이렉트 보험은 ~"</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>적용 예 / 출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>제공된 자료 기준으로는 ~</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>(삭제 후 바로 본론) ~</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>"제공된 자료 기준으로는 다이렉트 보험은 ~" → "다이렉트 보험은 ~" (No.3, 13, 16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>A-2</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>제공된 자료에는 / 제공 자료에서는 ~</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>(삭제) ~</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>No.10, 12, 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>A-3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>제공된 내용의 관점에서는 ~</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>(삭제) ~</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>No.6 — 밸루가 빨간색 지적 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>A-4</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>제공된 약관 예시들에서는 / 제공된 약관 내용에는 ~</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>약관에서는 ~ / 약관상 ~</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>No.4, 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>A-5</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>학습한 자료에 따르면 ~</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>(삭제) ~</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>"학습한 자료에 따르면 전동킥보드는 ~" → "전동킥보드는 ~"</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>제공된 내용의 관점에서는 ~</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>A-6</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>자료에 따르면 ~</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>(삭제) ~</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>QA No.6 지적 문구</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>2-4</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>No.3에서 4회 반복 출현</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>A-7</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>자료상 ~ / 자료 기준 ~</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>(삭제) ~</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>No.10, 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>A-8</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>자료에 명시된 내용 / 자료에 등장한 / 자료에 나온 ~</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>(삭제) ~</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>No.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>A-9</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>질의응답 기준으로는 ~</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>(삭제) ~</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>No.8 지적 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>A-10</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>자료에 포함된 예시는 아래와 같습니다</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>대표적으로 아래 상품이 있습니다</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>No.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="27" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>B-1</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>~것으로 안내되어 있습니다</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>~입니다 / ~할 수 있습니다</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>"단독설계가 가능한 것으로 안내되어 있습니다" → "단독으로 가입하실 수 있습니다"</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>2-5</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>"단독설계가 가능한 것으로 안내되어 있습니다" → "단독으로 가입하실 수 있습니다" (No.10, 11, 13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>B-2</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>~라고 정리되어 있습니다</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>~입니다</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>2-6</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>No.11, 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>B-3</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>~고 되어 있습니다 / ~로 되어 있습니다</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>~입니다</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>No.10에서 7회, No.11에서 4회 — 가장 빈번한 전언체</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>B-4</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>~내용이 확인됩니다 / ~이 확인됩니다</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>~이 있습니다 / ~입니다</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>2-7</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>~고 되어 있습니다</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>No.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>B-5</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>~라고 안내하고 있습니다</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>~입니다</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>2-8</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>질의응답 기준으로는 ~</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>(삭제) ~</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>QA No.8 지적 문구</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>2-9</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>B-6</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>~는 취지입니다 / ~라는 관점입니다</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>~입니다</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>No.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>확정할 근거가 부족합니다</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>정확히 안내드리려면 ○○ 확인이 필요합니다</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>QA No.12 지적 문구</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>2-10</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>No.12 지적 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>C-2</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>학습한 자료만으로는 확인할 수 없습니다</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>가입하신 증권(또는 약관)에서 ○○ 항목을 확인해 주시면 정확히 안내드릴 수 있습니다</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>C-3</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>현재 제공된 정보에 구체적인 안내가 없어 확인이 어렵습니다</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>이 부분은 담당 부서(○○팀) 확인이 필요한 내용입니다</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>2-11</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>학습한 자료만으로는 확인할 수 없습니다</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>가입하신 증권(또는 약관)에서 ○○ 항목을 확인해 주시면 정확히 안내드릴 수 있습니다</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>2-12</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>자료에 포함된 예시는 아래와 같습니다</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>대표적으로 아래 상품이 있습니다</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="42" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>이 부분은 담당 부서(○○팀)에 확인이 필요한 내용입니다</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>No.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>C-4</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>현재 학습된 내용에는 ~ (답변 본문이 있는데도 말미에 덧붙는 경우)</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>(삭제) — 답변을 전혀 생성하지 못한 경우에만 단독 출력</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>No.12, 16 — fallback 중복 출력</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>C-5</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>자료에 직접적인 안내가 없어 확답이 어렵습니다</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>이 기능은 시스템 담당 부서 확인이 필요합니다. ○○로 문의해 주시기 바랍니다</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>No.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40.5" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>원칙 3. 답변 구조 템플릿 (기대답변 16건에서 공통 추출)</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>구성 요소</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>작성 규칙</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>예시 문장</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="50" ht="27" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>공감 한 문장 (사고·질병·손해 문의일 때만)</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>1문장 이내. 형식적 사과가 아닌 상황 공감.</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>"많이 놀라셨겠어요. 팔이 부러질 정도면 통증도 심하고 일상생활도 불편하실 텐데요."</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="51" ht="27" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>두괄식 결론</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>"결론부터 말씀드리면, ~" 으로 시작하고 첫 3줄 안에 답을 준다.</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>"결론부터 말씀드리면, 보험 처리가 가능합니다. 다만 어떤 킥보드를 탔느냐에 따라 차이가 있습니다."</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="52" ht="27" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>근거·구분 (번호 2~4개)</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>조건이 갈리는 지점을 번호로 나눈다. 각 항목 아래 불릿 + 구체 수치.</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>"1. 자가 킥보드를 타다 다친 경우 / 2. 공유 킥보드를 타다 다친 경우"</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>비교표 (선택)</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>선택지가 2개 이상이면 표로 한눈에 정리.</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>"구분 | 신경성형술 등 | 척추 내시경 수술"</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>⚠️ 주의 또는 💡 요약 (택1)</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>리스크가 있으면 ⚠️ 주의, 없으면 💡 한 줄 요약으로 마무리.</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>"💡 암진단비 = 초기 목돈 / 암주요치료비 = 무한 리필 치료비 방패"</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="55" ht="27" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>다음 행동 안내</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>필요 서류·확인처·연락처 등 고객이 바로 할 수 있는 행동을 제시.</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>"서류 준비: 진단서(골절 분류코드 S42, S52 등), 치료비 영수증, 앱 이용 기록 캡처"</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="56" ht="27" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>마무리 권유 (선택)</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>단정 대신 권유형으로 닫는다.</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>"우선은 치료에 전념하시고, 통증이 가라앉으시면 보험사에 연락해 보시길 권해 드립니다."</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="57" ht="27" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>원칙 4. Before / After 실제 예시</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>QA 번호</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>Before (현재 출력)</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>After (권장)</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>변경 포인트</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="59" ht="162" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>No.11
 실비 단독설계</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>### 결론부터 말씀드리면
 - 현재 실손의료보험(실비)은 "단독으로 가입(설계)"이 가능한 상품이 있습니다.
@@ -2320,7 +2801,7 @@
 - 또한 제공된 자료(예: 흥국화재 무 실손의료보험 분석)에서도 "단독설계(특약 없이 실손만 가입 가능)" 형태가 가능한 것으로 안내되어 있습니다.</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>결론부터 말씀드리면, 실손의료보험은 지금도 단독으로 가입하실 수 있습니다.
 1. 단독 가입이 가능한 상품
@@ -2332,7 +2813,7 @@
 나이와 직업, 최근 치료 이력만 알려주시면 가능한 방향으로 안내해 드리겠습니다.</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>· 출처 언급 3회 전부 삭제
 · 상품명은 그대로 살림
@@ -2341,21 +2822,21 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="60" ht="162" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>No.13
 고양이 펫보험</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>### 결론: 동물등록증(등록번호) 없이도 가입 "가능한 경우"가 있습니다
 - 제공된 자료 기준으로는 동물등록번호가 없어도 '사진 제출' 방식으로 진행되는 케이스가 확인됩니다.
 - 제공된 약관 내용(KB 고양이 펫보험)에는 등록 여부에 따라 제출서류가 달라지는 기준이 확인됩니다.</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>결론부터 말씀드리면, 동물등록증이 없어도 가입하실 수 있는 경우가 있습니다.
 1. 등록번호 대신 사진으로 대체됩니다
@@ -2366,7 +2847,7 @@
 고양이 나이와 중성화 여부, 병력 유무를 알려주시면 가입 가능한 상품으로 좁혀 안내해 드리겠습니다.</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>· "제공된 자료 기준으로는" 삭제
 · "~확인됩니다" → "~합니다"
@@ -2374,45 +2855,543 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="61" ht="94.5" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>No.6
 클레임 대응</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>### 무조건 "죄송합니다"라고 사과해야 하나요?
-- 제공된 내용의 관점에서는 무조건적인 사과("죄송합니다" 반복)는 권하지 않습니다.</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
+- 제공된 내용의 관점에서는 무조건적인 사과("죄송합니다" 반복)는 권하지 않습니다.
+- 이유는, 형식적인 사과가 오히려 무성의하게 느껴질 수 있고, 이후에 효과적인 질문을 통해 구체 정보를 얻는 흐름을 막을 수 있다는 취지입니다.</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>무조건적인 사과를 반복하는 것은 권해 드리지 않습니다.
-형식적인 사과는 오히려 무성의하게 느껴질 수 있고, 고객에게서 구체적인 정보를 얻어낼 기회를 막기 때문입니다.</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>· "제공된 내용의 관점에서는" 삭제 (빨간색 지적 문구)</t>
+형식적인 사과는 오히려 무성의하게 느껴질 수 있고, 고객에게서 구체적인 정보를 얻어낼 기회를 막기 때문입니다.
+대신 "죄송합니다"가 아니라 "고맙습니다"로 시작해 보십시오.
+"정말 감사합니다. 바쁘신 와중에도 저희 잘못을 지적해 주신 데 대한 감사의 표시입니다. 말씀하신 사항을 반드시 적용하겠습니다."</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>· "제공된 내용의 관점에서는" 삭제 (밸루가 빨간색 지적 문구)
+· "~라는 취지입니다" → "~때문입니다"</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="175.5" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>No.3
+다이렉트 보험</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>- 제공된 자료 기준으로 다이렉트 보험은 보험사가 고객에게 직접 판매하는 방식이라서, 원칙적으로는 고객 본인이 직접 가입하는 구조입니다.
+  (자료에 따르면, 일부 보험비교사이트는 대리점이 운영하며 …)
+- 자료에 따르면 '보험다모아'는 손해보험협회와 생명보험협회가 함께 운영하는 비교 서비스로 …
+- 자료에 따르면 보험사별로 보험료 차이가 있을 수 있어 …</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>다이렉트 보험은 보험사가 고객님께 직접 판매하는 방식이라, 원칙적으로는 고객님이 직접 가입하시는 구조입니다.
+다만 담당 설계사가 보내드린 가입 링크를 통해서도 다이렉트 가입이 가능합니다.
+어느 보험사가 되는지 확인하는 방법
+• 보험다모아(온라인 보험슈퍼마켓): 손해보험협회와 생명보험협회가 함께 운영하는 비교 서비스입니다. 자동차·실손·여행자·연금·어린이/태아·암·보장성·저축성 등 8개 상품의 보험료를 실시간으로 비교하고, 상품을 고르시면 해당 보험사 홈페이지로 바로 이동해 가입하실 수 있습니다.
+• 보험사별 다이렉트 홈페이지: 회사마다 보험료 차이가 있어 직접 비교해 보시는 편이 정확합니다.
+⚠️ 다이렉트가 항상 저렴한 것은 아닙니다. 설계사 수당이 빠져 대체로 저렴하지만, 손해율이 높은 일부 보험사의 다이렉트 상품은 비교사이트보다 비쌀 수도 있습니다.</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>· 출처 언급 11회 전부 삭제
+· 누락됐던 "설계사 링크로 가입 가능" 사실 추가 (기대 답변 반영)
+· 정보량은 그대로 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="216" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>No.10
+통풍환자 보험</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>- 제공된 자료 기준으로는 통풍 관련 보장을 담은 상품/특약이 존재하며 …
+### 1) 통풍 진단비(특약)로 대비하는 방법
+- 자료에 따르면 통풍 보장은 보통 다음과 같은 형태로 존재합니다.
+- 또한 KDB라이프 상품요약서 발췌 내용에는 "통풍진단특약N(무)"가 있으며, … 지급하는 구조가 안내되어 있습니다.
+- 장점으로 자료에 명시된 내용: …</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>통풍이 있으셔도 가입하실 수 있는 보험이 있습니다.
+1. 통풍 진단비 특약이 있는 상품
+• KDB라이프핏건강보험(무) — 통풍진단특약N(무): 보험기간 중 통풍(질병분류코드 M10)으로 진단 확정 시 최초 1회에 한해 지급합니다. (특약가입금액 100만 원 기준)
+• DB손해보험 참좋은종합보험: 특약 항목에 통풍 진단비가 포함되어 있습니다.
+2. 병력이 있으셔도 가입 문턱이 낮은 간편심사 상품
+• DB손보 무배당 프로미라이프 2Q초간편 건강보험: 2가지 질문으로 가입, 90세까지 가입 가능
+• DB손보 1Q 초간편 건강보험: 고지 항목을 1가지 질문으로 축소
+💡 함께 보시면 좋습니다: 통풍 환자 중 심혈관질환 초고위험군에 속하는 비율이 있어, 협심증·급성심근경색증 등 심혈관질환 진단비도 같이 검토해 보시길 권해 드립니다.
+최근 진단·입원·수술 시점과 현재 복용 중인 약이 있으신지 알려주시면 가입 가능한 상품으로 좁혀 안내해 드리겠습니다.</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>· 출처 언급 19회 전부 삭제 (최다 발생 건)
+· 밸루가 지적 반영: "통풍 진단비로 대비하는 방법" → 상품명 특정("KDB라이프핏건강보험(무)")
+· 소제목을 기능 설명이 아닌 고객 관점으로 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="121.5" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>No.12
+실비 만기</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>- 제공된 자료에는 특정 보험사/상품을 비교해서 "어디 상품이 만기가 제일 길다"를 단정할 수 있는 전체 상품 비교표가 없습니다.
+- "어느 회사/어느 상품이 100세 만기인지"를 특정해 드리기에는, 현재 제공된 자료만으로는 상품명/보험사별 현행 판매 상품을 확정할 근거가 부족합니다.
+(…본문 답변 뒤에…)
+현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다. 다른 주제 또는 조금 더 구체적으로 질문해 주시기 바랍니다. …</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>실비보험 만기는 현재 100세 만기가 가장 깁니다.
+과거에는 80세 만기가 일반적이었으나 보장기간이 확대되면서 지금은 100세 만기 구성까지 나와 있습니다.
+다만 어느 보험사 상품이 100세 만기인지는 판매 시점에 따라 수시로 바뀝니다. 아래 세 가지만 알려주시면 현재 판매 중인 100세 만기 상품으로 좁혀 비교해 드리겠습니다.
+1. 원하시는 기준이 보장만기(100세)인지, 갱신주기(1년/3년/5년)인지
+2. 단독 실손으로 가입하실 것인지, 종합보험에 실손특약을 포함하실 것인지
+3. 현재 가입 중이신 실손이 있으시면 보험사·상품명·가입년도</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>· 출처 언급 10회 삭제
+· "확정할 근거가 부족합니다"(시스템 한계) → "알려주시면 좁혀 드리겠습니다"(고객 행동)
+· 답변이 생성됐으므로 말미 fallback 문구 제거 (원칙 1-7)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A48:D48"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>프롬프트 삽입 문구 초안 — 아래 블록을 시스템 프롬프트에 그대로 반영 요청드립니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>적용: FA AI / Orca AI 공통 · 근거: [3_답변어투가이드] 원칙 1~2 · 문구는 iFA 초안이며 밸루가측 검토 후 조정 가능합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="700" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>프롬프트 본문
+(복사용)</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>[답변 어투 규칙]
+1. 당신은 고객에게 직접 말하는 보험 상담사입니다. 검색 결과를 요약해 보고하는 것이 아닙니다.
+   답변은 사내 문서를 정리한 보고서가 아니라, 상담사가 고객에게 건네는 말이어야 합니다.
+2. 지식의 출처가 내부 문서라는 사실을 문장에 드러내지 마십시오.
+   아래 표현은 어떤 경우에도 사용하지 않습니다. 해당 구절은 삭제하고 바로 본론으로 들어갑니다.
+   - "제공된 자료", "제공된 내용", "제공된 약관", "제공 자료"
+   - "학습한 자료", "학습된 내용", "학습 자료"
+   - "자료에 따르면", "자료상", "자료 기준으로는", "자료에는", "자료에 명시된", "자료에 등장한"
+   - "질의응답 기준으로는"
+3. 전언체를 쓰지 말고 단정체로 서술하십시오.
+   - "~라고 되어 있습니다", "~것으로 안내되어 있습니다", "~라고 정리되어 있습니다",
+     "~이 확인됩니다", "~라는 취지입니다"
+   → "~입니다", "~할 수 있습니다", "~때문입니다"
+4. 첫 문장은 결론입니다. "결론부터 말씀드리면, ~" 형태로 시작하고 3줄 안에 답을 제시하십시오.
+   배경 설명과 조건 분기는 결론 뒤에 둡니다.
+5. 확인이 필요한 경우, 시스템의 한계가 아니라 고객이 할 행동으로 표현하십시오.
+   - (X) "확정할 근거가 부족합니다"
+   - (X) "학습한 자료만으로는 확인할 수 없습니다"
+   - (O) "정확히 안내드리려면 가입하신 상품명 확인이 필요합니다"
+   - (O) "증권의 담보명 부분을 알려주시면 정확히 안내드리겠습니다"
+6. 근거 문서에 상품명·회사명·팀명·연락처 등 고유명사가 있으면 반드시 그대로 특정해 안내하십시오.
+   - (X) "통풍 진단비 특약이 있는 상품이 존재합니다"
+   - (O) "KDB라이프핏건강보험(무)의 통풍진단특약N(무)이 있습니다"
+7. 근거 문서에 없는 제약·금지·예외를 추론해서 단정하지 마십시오.
+   문서에 "개별 제작이 가능하다"고만 되어 있으면 "임의 제작은 불가"라고 확장하지 않습니다.
+8. 본문 답변을 생성한 경우, 말미에 "현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다 …"
+   안내문을 덧붙이지 마십시오. 이 안내문은 답변을 전혀 생성하지 못한 경우에만 단독으로 출력합니다.
+9. 마크다운 헤딩(###)과 볼드(**)를 과도하게 사용하지 말고,
+   번호(1. 2. 3.)와 불릿(•) 중심의 상담 문장으로 작성하십시오.
+10. 질문에 사고 경위가 명시된 경우, 그 경위와 무관한 담보를 함께 안내하지 마십시오.
+    (예: "요리하다 화상" 질문에 교통상해 화상진단비를 병기하지 않습니다.)
+11. 답변 마지막은 고객이 바로 할 수 있는 행동으로 닫으십시오.
+    필요 서류, 확인처, 문의할 부서·연락처, 또는 추가로 알려주셔야 할 정보를 제시합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>적용 후 기대 효과</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>· 출처 언급 어투 9건 → 0건
+· fallback 중복 출력 2건(No.12, 16) 해소
+· 상품명 미특정 1건(No.10) 해소
+· 무관 담보 병기 1건(No.4) 재발 방지
+· 근거 없는 단정 1건(No.8) 재발 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>유지 요청 사항</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>학습된 내용을 전혀 찾지 못한 경우의 기존 fallback 안내문은 현행 그대로 유지해 주시기 바랍니다.
+("현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다. 다른 주제 또는 조금 더 구체적으로 …")
+해당 문구 자체는 문제가 없으며, 답변이 생성됐는데도 함께 붙는 경우만 조정 대상입니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>어투 검수 체크리스트 — 프롬프트 반영 후 재검증 시 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>재검증 대상: 답변이 생성된 9건 (No.3, 4, 6, 8, 10, 11, 12, 13, 16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>검수 항목</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>판정 기준</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>자동 검출 키워드</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>출처 언급 문구가 없는가</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>아래 키워드가 답변에 1회도 등장하지 않으면 통과</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>제공된 자료 / 제공된 내용 / 제공된 약관 / 제공 자료 / 학습한 자료 / 학습된 내용 / 자료에 따르면 / 자료상 / 자료 기준 / 자료에는 / 자료에 명시 / 질의응답 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>전언체가 아닌 단정체인가</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>아래 어미가 등장하지 않으면 통과</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>되어 있습니다 / 안내되어 있습니다 / 정리되어 있습니다 / 확인됩니다 / 라는 취지입니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>첫 3줄 안에 결론이 제시되는가</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>첫 문단에 "가능합니다 / 어렵습니다 / ~입니다" 형태의 답이 있으면 통과</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>결론부터 말씀드리면</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>시스템 한계를 노출하지 않는가</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>고객 행동 요청 형태로 표현됐으면 통과</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>근거가 부족 / 확인할 수 없습니다 / 확답이 어렵습니다 / 확정할 수 없습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>고유명사가 특정되어 있는가</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>근거 문서에 상품명·팀명이 있으면 답변에도 그대로 등장해야 통과</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>(수동 확인) 상품 / 특약 / 팀 언급 시 명칭 유무</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>fallback이 중복 출력되지 않는가</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>본문 답변이 있으면 말미 안내문이 없어야 통과</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>현재 학습된 내용에는 (본문 길이 200자 초과 시 동시 출현 여부)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>근거 없는 단정이 없는가</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>원문에 없는 금지·제약 표현을 만들지 않았으면 통과</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>(수동 확인) 불가 / 안 됩니다 / 해서는 안 / 필수입니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>무관한 담보를 병기하지 않았는가</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>질문의 사고 경위와 다른 담보가 안내되지 않으면 통과</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>(수동 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>마무리에 행동 안내가 있는가</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>필요 서류·확인처·추가 문의 정보 중 하나가 제시되면 통과</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>(수동 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>※ 1·2·4·6번 항목은 키워드 매칭으로 자동 검출이 가능합니다. 재검증 시 답변 전문을 대상으로 키워드 스캔 후, 5·7·8·9번만 수동 확인하시면 효율적입니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2428,7 +3407,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>밸루가 전달용 톤 레퍼런스 — D열(기대 답변)이 iFA가 목표하는 답변 어투입니다. [3_답변어투가이드]와 함께 참고해 주시기 바랍니다.</t>
         </is>
@@ -3138,7 +4117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3155,7 +4134,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>밸루가 요청 회신란 — 아래 노란색 셀(D·E열)을 iFA에서 작성해 주세요</t>
         </is>
@@ -3196,34 +4175,34 @@
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>(예시)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>전동킥보드를 타다 팔이 골절됐는데, 보험 처리가 되나요?</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>Cloud</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>영업 1팀_5차 손해보험 소비자상담 주요 사례집 117건(1170확장판)_00586687.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -3231,7 +4210,7 @@
           <t>사망보험금 1억 받으면 상속세 내야 하나요? 보험금도 상속 재산에 포함되나요?</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3240,7 +4219,7 @@
       <c r="E5" s="7" t="n"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -3248,7 +4227,7 @@
           <t>전동킥보드를 타다 팔이 골절됐는데, 보험 처리가 되나요?</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3257,7 +4236,7 @@
       <c r="E6" s="7" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -3265,7 +4244,7 @@
           <t>금리가 오르면 전세가 유리할까요, 월세가 유리할까요?</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3274,7 +4253,7 @@
       <c r="E7" s="7" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -3282,7 +4261,7 @@
           <t>같은 나이라도 사람마다 보험 설계가 달라지는 거야?</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3291,7 +4270,7 @@
       <c r="E8" s="7" t="n"/>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -3299,7 +4278,7 @@
           <t>허리디스크 시술 받으려는데 내시경 시술이랑 수술이랑 보험 보장 금액이 다른가요?</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3308,7 +4287,7 @@
       <c r="E9" s="7" t="n"/>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -3316,7 +4295,7 @@
           <t>변액보험 펀드 종류가 너무 많은데, 뭘 골라야 하는 거야?</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3325,7 +4304,7 @@
       <c r="E10" s="7" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -3333,7 +4312,7 @@
           <t>1세대 1주택자의 장기보유특별공제에서 2년 거주 요건을 채우지 못하면 어떤 공제율이 적용되는가?</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3342,7 +4321,7 @@
       <c r="E11" s="7" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -3351,7 +4330,7 @@
 </t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3360,7 +4339,7 @@
       <c r="E12" s="7" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -3368,7 +4347,7 @@
           <t>무배당 KB스타재해사망보험 1년 만기 때 사고가 없었으면 그동안 낸 보험료에서 배당금을 받을 수 있나요?</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3377,7 +4356,7 @@
       <c r="E13" s="7" t="n"/>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -3385,7 +4364,7 @@
           <t>암주요치료비 왜 필요해?</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3394,7 +4373,7 @@
       <c r="E14" s="7" t="n"/>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -3402,7 +4381,7 @@
           <t>간염 진단비 나오는 보험이 있나요?</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3411,7 +4390,7 @@
       <c r="E15" s="7" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -3419,7 +4398,7 @@
           <t>아파트 안에 골프연습장에서 넘어졌는데 보험금 받을 수 있어?</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3428,7 +4407,7 @@
       <c r="E16" s="7" t="n"/>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -3436,7 +4415,7 @@
           <t>소득세법상 '거주자'의 정의는 무엇인가요?</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3445,7 +4424,7 @@
       <c r="E17" s="7" t="n"/>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -3453,7 +4432,7 @@
           <t>운전자보험 특약 설명해줘</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3462,7 +4441,7 @@
       <c r="E18" s="7" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -3470,7 +4449,7 @@
           <t>메디코드는 어떤 서비스인가요?</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>
@@ -3479,7 +4458,7 @@
       <c r="E19" s="7" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -3487,7 +4466,7 @@
           <t>어제 길거리 공유 킥보드 타다가 넘어져서 팔이 부러졌는데요. 내가 든 실비 보험에서 병원비 받을 수 있나요? 킥보드는 처음 타본 거예요</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>개선필요</t>
         </is>

--- a/valuega/밸루가_QA검증요청_회신초안_20260812.xlsx
+++ b/valuega/밸루가_QA검증요청_회신초안_20260812.xlsx
@@ -7,16 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_요청사항요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_QA건별회신" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3_답변어투가이드" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3-1_프롬프트문구초안" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3-2_어투검수체크리스트" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4_모범답변예시" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="5_데이터확인필요_회신" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="0_참고_품질개선보고서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1_요청사항요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2_QA건별회신" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3_답변어투가이드" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3-1_프롬프트문구초안" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3-2_어투검수체크리스트" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="4_모범답변예시" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="5_데이터확인필요_회신" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2_QA건별회신'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_QA건별회신'!$A$1:$J$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,6 +101,12 @@
       <color rgb="00808080"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00375623"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -159,13 +166,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -178,12 +191,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -567,6 +574,693 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>[참고자료] AI 답변 품질 개선 종합 보고서 — 19개 케이스 분석 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>원본: AI 답변 품질 개선 종합 보고서(HTML) · 케이스 1~16은 본 워크북 [5_데이터확인필요_회신]의 16건과 동일 · 케이스 17~19는 본 QA검증요청에 미포함된 추가 건</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>보고서 결론 — 품질 문제의 원인 구성</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>비중</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>원인</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>해결 경로</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>70~80%</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>프롬프트 설정 문제</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>결론 후배치, '학습한 자료에 따르면' 반복, 나열 구조 등</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>즉시 수정 가능 → [3-1_프롬프트문구초안]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>일부</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>모델 학습 방식</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>LLM은 기본적으로 정보를 빠짐없이 전달하려는 방향으로 학습됨</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>프롬프트로 제어 가능하나 완전 교정은 어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>일부</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>학습 데이터 문제</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>케이스 15(메디코드)처럼 학습 정보 자체가 부족한 경우</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>RAG 또는 데이터 보강으로만 해결 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>※ 보고서 결론: 19개 케이스에서 발견된 문제의 대부분은 프롬프트로 해결됩니다. 프롬프트 수정을 먼저 적용하고, 효과를 확인한 뒤 추가 대응 방향을 잡는 것이 현실적인 순서입니다.</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>19개 케이스 누적 감점 패턴 (보고서 원문)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>감점 패턴</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>발생 횟수</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>심각도</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>결론이 마지막에 위치</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>13/19 케이스</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>고객이 읽다 지쳐 핵심을 놓침 — 첫 문장에 결론 선제 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>'학습한 자료에' 반복</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>13/19 케이스 (최대 6회)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>AI 학습 기반임을 스스로 노출해 신뢰도 저하 — 자연스러운 서술로 대체</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>가진 정보를 전달 못 함</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>케이스 5, 11, 14, 18, 20</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>회사 AI가 더 많은 정보를 보유하고도 나열 구조로 인해 핵심이 묻히는 패턴 반복</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>고객 정보 미활용</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>케이스 16, 17</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>고객이 제공한 힌트('처음 탔다', '약 2년 복용')를 반영하지 않아 일반 답변이 됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>나열 구조로 핵심 매몰</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>케이스 6, 10, 14, 20</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>항목 나열이 많을수록 "그래서 나는 어떻게 해야 하나"가 읽히지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>숫자·비유 없는 추상 설명</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>케이스 3, 6, 8, 10</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>정보는 있어도 숫자 시뮬레이션·비유 없이 서술만 하면 체감이 안 됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>전략 요약 없음</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>케이스 4, 10, 20</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>"그래서 내 상황에 뭐가 유리한가"라는 핵심 요약이 없거나 마지막에 묻힘</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>행동 요령 부재</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>케이스 5, 6, 8, 11, 12, 16</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>사고·청구 질문에서 "지금 당장 해야 할 것"이 반복적으로 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>보험 종류별 미분화</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>케이스 19</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>종류에 따라 답이 달라지는 질문을 단일 답변으로 처리해 부정확해짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>과장·단정적 표현</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>케이스 17 (원하는 답변 형식)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>'100% 가입 가능' 단정 — 보험 AI 금지 표현으로 별도 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>약관 원문 직접 인용</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>케이스 9</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>고객 언어로 요약·설명해야 할 내용을 법조문 그대로 인용</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>최종 인사이트 6가지 (보고서 원문)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>과제</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>해결 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>'학습한 자료에' 표현 전면 제거</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>13/19 케이스에서 반복, 최대 6회 등장. 시스템 프롬프트 고정 없이는 지속 재등장합니다.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>시스템 프롬프트</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>결론을 첫 문장으로</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>결론이 마지막에 위치. 전 질문 유형 공통 감점 요인입니다.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>시스템 프롬프트</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>고객 제공 정보 즉시 활용</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>케이스 16·17처럼 고객이 제공한 개인화 정보를 반영하지 않는 패턴. 고객의 말에서 힌트를 읽어야 합니다.</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>답변 생성 방식</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>숫자·비유로 직관화</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>추상적 설명 대신 금액·기간 시뮬레이션과 비유 1개 추가 시 체감도가 즉시 향상됩니다.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>구조</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="27" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>고유 정보를 구조로 살리기</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>회사 AI만 아는 정보(한도 수치, 약관 구조 등)가 나열 구조에 묻히는 패턴 반복. 표나 별도 섹션으로 부각해야 합니다.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>구조</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>자사 서비스 학습 데이터 보강</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>케이스 15에서 자사 서비스(메디코드)를 외부 검색 기반 답변이 더 상세하게 안내. 프롬프트 개선만으로는 해결되지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>학습 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40.5" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>※ ①②만 시스템 프롬프트에 고정해도 전체 품질이 즉시 향상됩니다. ③은 답변 생성 방식, ④⑤는 구조, ⑥은 학습 데이터 레벨에서 해결해야 합니다.</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="40.5" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>[참고] 회사 AI 우세 케이스: 케이스 7(장기보유특별공제) · 케이스 13(소득세법 거주자 정의). 공통점은 법령·세법 정의 유형입니다.</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="27" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>밸루가 전달 전 확인 필요 — 보고서 내 수치 불일치 2건</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>조치</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="27" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>누적 감점 패턴 표 3개 행</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>'케이스 20'이 3회 언급되나(가진 정보를 전달 못 함 / 나열 구조로 핵심 매몰 / 전략 요약 없음), 보고서에 수록된 케이스는 1~19번까지입니다.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>케이스 번호 확인 후 수정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>감점 패턴 표 vs 최종 인사이트 ②</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>'결론이 마지막에 위치'가 표에서는 13/19, 최종 인사이트에서는 13/18로 서로 다르게 표기되어 있습니다.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>분모 통일 필요</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A32:D32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -587,65 +1281,66 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>원본: 260729 QA검증요청 (3개 시트) · 대상 로그: 2026-03-08 ~ 03-10 · 노란색 셀 = iFA 작성/확정 필요</t>
+          <t>원본: 260729 QA검증요청 (3개 시트) · 대상 로그: 2026-03-08 ~ 03-10 · 참고자료: AI 답변 품질 개선 종합 보고서(19개 케이스) → [0_참고_품질개선보고서] · 노란색 셀 = iFA 작성/확정 필요</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>밸루가 요청 내용</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>iFA 조치 사항</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>담당/상태</t>
         </is>
       </c>
     </row>
     <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>① 답변 어투</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>"원하시는 답변 톤이나 문장 예시를 함께 전달해주시면 검토에 도움이 될 것 같습니다."
 → 프롬프트 개선은 이미 반영, 다만 기준이 될 톤·예시 문장을 iFA가 제공해달라는 요청</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>4건
 (No.6, 11, 12, 13)</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>· [3_답변어투가이드] 금지표현 사전(21개) + 답변 구조 템플릿 + Before/After 6건
-· [3-1_프롬프트문구초안] 그대로 반영 가능한 프롬프트 블록 11개 규칙
+· [3-1_프롬프트문구초안] 품질개선 보고서 프롬프트 지침 + QA 실측 보강분 통합본
 · [3-2_어투검수체크리스트] 반영 후 재검증용 (키워드 자동 검출 가능)
 · [4_모범답변예시] 기대답변 16건을 톤 레퍼런스로 함께 전달
-※ 실측: 밸루가 분류 4건이 아니라 답변 생성 9건 전부에서 발생 중</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+※ 실측: 밸루가 분류 4건이 아니라 답변 생성 9건 전부에서 발생 중
+※ 품질개선 보고서 기준으로도 13/19 케이스에서 동일 패턴 확인</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>iFA → 밸루가
 (본 문서로 회신 가능)</t>
@@ -653,120 +1348,120 @@
       </c>
     </row>
     <row r="6" ht="78" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>② 데이터 확인</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>"빨간색으로 표시된 참조 문서코드(ID) 기준으로 조회가 되지 않아 원본 문서명 확인이 필요합니다.
 해당 질문이 실제로 어떤 문서/파일을 기준으로 답변되어야 하는지도 함께 부탁드립니다."</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>3건
 (No.7, 8, 9)</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>· 3건 모두 기준 문서 특정 완료 → [2_QA건별회신] 참조
 · 문서코드(ID) 조회 불가 건은 학습 인덱스 재확인 필요 (밸루가측)</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>iFA 회신 → 밸루가 재확인</t>
         </is>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>③ 기타 (정책 결정)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>"일반상식 내용에 대해서 워크플로우 처리하여 웹검색으로 가능한지,
 아니면 사용자가 직접 웹검색 버튼 누르고 검색하도록 할지 방안 선택 필요"</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>1건
 (No.14 드림케어겔)</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>· iFA 정책 결정 필요 (자동 웹검색 vs 사용자 트리거 버튼)
 · 권고: 1단계는 "웹검색으로 확인하기" 버튼 노출 방식 (오답·출처 리스크 최소화)</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>iFA 의사결정 필요</t>
         </is>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>④ 미회신 (밸루가 회신 대기)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>밸루가측 요청사항 공란 — 1차 확인 결과만 기재된 건</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>7건
 (No.2,3,4,5,10,15,16)</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>· 학습데이터 보강 / 재현성 확인 등 후속 조치 필요
 · [2_QA건별회신] 시트에 건별 회신 초안 작성</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>iFA → 밸루가</t>
         </is>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>⑤ 데이터확인필요 시트 (별건)</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>"어떤 채널에서 질의를 하셨는지 알려주시면 감사하겠습니다. (Cloud/Link)"
 "기대하시는 답변이 어떤 문서를 기준으로 답이 만들어져야 하는지 원본 문서를 알려주시면 감사하겠습니다."</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>16건
 (전 건)</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>· 질의 채널(Cloud / Link) 확정 필요
 · 기대답변의 근거 원본 문서명 16건 전부 기재 필요
 → [5_데이터확인필요_회신] 시트 작성 필요</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>iFA 작성 필요 (미완)</t>
         </is>
@@ -781,7 +1476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -803,289 +1498,289 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>AI채널</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>로그ID</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>결과</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>사용자 질문</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>문제 요약(1차확인)</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>밸루가측 요청사항</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>iFA 회신 초안</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>조치 주체</t>
         </is>
       </c>
     </row>
     <row r="2" ht="118" customHeight="1">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>FA AI</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>43657</v>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>응답실패</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>계단에서 넘어져서 팔 골절상을 입었어, 보험처리가 가능할까?</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>일반 상해·골절 관련 학습데이터 부재. (이륜자동차보험/체외충격파/실손 맥락의 골절 내용만 존재)</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>일반 상해(골절·염좌·타박 등) 기본 상담 데이터를 iFA에서 추가 등록 예정입니다.
 · 등록 전까지는 fallback 문구 대신, 보유 담보(실손·골절진단비·상해수술비) 기준의 일반 안내로 연결 가능한지 검토 요청드립니다.
 · 참고 기대답변: [4_모범답변예시] No.2 / No.16 (킥보드 골절 케이스)</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>데이터 보강</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>iFA 데이터 등록 → 밸루가 재검증</t>
         </is>
       </c>
     </row>
     <row r="3" ht="118" customHeight="1">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>FA AI</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>43713</v>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>응답부족</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>담당 설계사가 다이렉트 보험도 가입해줄수 잇다고 하던데, 보험사 어디가 돼?</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>"담당 설계사가 제공한 링크로 다이렉트 가입 가능"이라는 핵심 안내 누락. FA AI에 다이렉트 자동차보험 자료 없음 (공통학습데이터 「영업 1팀_5차 손해보험 소비자상담 주요 사례집 117건(1170확장판)_00586687.xlsx」의 보험다모아 내용만 존재)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>"설계사가 제공한 다이렉트 가입 링크를 통해서도 가입 가능"하다는 내용은 현재 학습자료에 없어 iFA에서 원문 추가 등록하겠습니다.
 · 추가 등록 후 재검증 요청드립니다.
 · 아울러 답변 서두의 "제공된 자료 기준으로는" 표현은 [3_답변어투가이드] 기준으로 제거 부탁드립니다.</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>데이터 보강 + 어투</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>iFA 데이터 등록 → 밸루가 재검증</t>
         </is>
       </c>
     </row>
     <row r="4" ht="118" customHeight="1">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>FA AI</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>43712</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>응답부족</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>요리하다 불에 데였어. 화상 진단비 지급이 될까?</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>요리 중 화상 질문에 "교통상해 화상 진단비"까지 함께 안내. → 재질문 결과 해당 항목 사라짐(처리완료)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>재질문 시 해당 항목이 노출되지 않는 것으로 확인되어 종결 처리합니다.
 · 다만 질문에 사고 경위(요리 중)가 명시된 경우 무관한 담보(교통상해)를 병기하지 않도록 프롬프트에 조건 반영 여부만 확인 부탁드립니다.</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>종결</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>종결(확인만)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="118" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Orca AI</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>43707</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>응답부족</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>직원이 지각이나 조퇴를 여러 번 반복하여 그 합산 시간이 하루 근무 시간(8시간)을 넘겼습니다. 이 경우 하루를 결근한 것으로 처리해도 됩니까?</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>기대 답변란에 "자녀교육비 소득 80%/저축 20%" 내용이 기재되어 있어 질문과 무관. 시트 작성 오류로 판단됨.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>기재 오류로 보입니다. 해당 건의 기대 답변(자녀교육비 공식)이 질문과 무관하여 검증이 불가합니다.
 · 원 요청자에게 기대 답변 재확인 후 재제출하겠습니다. 금회 검증 대상에서는 제외 부탁드립니다.
 · 참고: AI 답변 자체(결근 처리 불가)는 노무 기준상 타당한 것으로 판단됩니다.</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>반려/재제출</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>iFA 원요청자 확인</t>
         </is>
       </c>
     </row>
     <row r="6" ht="118" customHeight="1">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Orca AI</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>43691</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>응답부족</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>고객이 불만을 제기하거나 화를 낼 때, 영업사원은 어떻게 대처해야 합니까? 무조건 죄송하다고 사과해야 하나요?</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>"제공된 내용의 관점에서는~" 등 출처를 언급하는 불필요한 서두 포함. 학습 내용을 찾지 못한 경우의 fallback 문구는 문제 없으나, 내용을 찾은 경우 "제공된 내용~", "학습된 내용~" 언급은 불필요.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>원하시는 답변 톤이나 문장 예시를 함께 전달해주시면 검토에 도움이 될 것 같습니다.</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>요청하신 톤·문장 예시를 [3_답변어투가이드] / [3-1_프롬프트문구초안] 시트로 전달드립니다.
 · 금지표현 사전(21개), 답변 구조 템플릿, Before/After 6건 포함
@@ -1094,51 +1789,51 @@
 · 유지 요청: 학습 내용을 찾지 못한 경우의 기존 fallback 안내 문구는 현행 유지가 맞습니다.</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>프롬프트 개선</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>밸루가 반영</t>
         </is>
       </c>
     </row>
     <row r="7" ht="118" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Orca AI</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>43482</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>응답실패</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>ifa 계약관리팀 전화번호</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>팀 명칭 오류: 계약관리팀(X) → 계약서비스팀(O). 더 큰 문제는 "계약서비스팀 전화번호"로 물어도 자료를 찾을 수 없다고 응답함.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>빨간색으로 표시된 참조 문서코드(ID) 기준으로 조회가 되지 않아 원본 문서명 확인이 필요합니다.
 해당 질문이 실제로 어떤 문서/파일을 기준으로 답변되어야 하는지도 함께 부탁드립니다.</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>[기준 문서] 스텝업무분장표_20260310_06443326.csv
 · 위 파일에 계약서비스팀 연락처가 기재되어 있습니다. 해당 문서 기준으로 답변되어야 합니다.
@@ -1146,51 +1841,51 @@
 · 요청 2: "계약관리팀 = 계약서비스팀" 동의어 매핑 추가 검토 부탁드립니다.</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>데이터확인</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>밸루가 색인 확인</t>
         </is>
       </c>
     </row>
     <row r="8" ht="118" customHeight="1">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Orca AI</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>43551</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>응답실패</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>명함은 회사 통해서만 만들어야해?</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>"사업단 또는 개인이 임의로 제작하는 것은 불가"는 학습 자료에 없는 내용을 AI가 추측하여 답변(할루시네이션). 실제 자료에는 "명함을 개별적으로 제작 할 수 있으나 회사에서 정한 가이드라인에 따라 제작하여야 합니다"로 기재. 또한 "질의응답 기준으로는"이라는 문구는 불필요.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>빨간색으로 표시된 참조 문서코드(ID) 기준으로 조회가 되지 않아 원본 문서명 확인이 필요합니다.
 해당 질문이 실제로 어떤 문서/파일을 기준으로 답변되어야 하는지도 함께 부탁드립니다.</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>[기준 문서] 준법감시팀_명함_20250821_09053209.csv
 · 원문: "명함을 개별적으로 제작 할 수 있으나 회사에서 정한 가이드라인에 따라 제작하여야 합니다."
@@ -1198,51 +1893,51 @@
 · 요청 2: "질의응답 기준으로는" 문구 제거 ([3_답변어투가이드] 준용)</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>데이터확인 + 어투</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>밸루가 색인 확인 + 프롬프트</t>
         </is>
       </c>
     </row>
     <row r="9" ht="118" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Orca AI</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>43468</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>응답부족</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>디비생명 수수료 환수율 알려줘</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>DB생명 기본환수는 18회차까지 존재하나 5회차까지만 응답. 표 데이터가 중간에서 잘려서 출력됨.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>빨간색으로 표시된 참조 문서코드(ID) 기준으로 조회가 되지 않아 원본 문서명 확인이 필요합니다.
 해당 질문이 실제로 어떤 문서/파일을 기준으로 답변되어야 하는지도 함께 부탁드립니다.</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>[기준 문서] iFA Cloud 공지 「[환수] 각 보험사 회차별 수당 환수율 (2024년 12월 기준)」
   https://m.ifacloud.co.kr/notice.aspx?sidx=2387
@@ -1250,249 +1945,249 @@
 · 요청: 표 형태 데이터가 상위 일부만 청킹되어 잘리는 것으로 보입니다. 표 단위 청킹(행 누락 방지) 검토 부탁드립니다.</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>데이터확인</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>밸루가 청킹 확인</t>
         </is>
       </c>
     </row>
     <row r="10" ht="118" customHeight="1">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>FA AI</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>43402</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>응답부족</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>통풍환자 가입가능 보험</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>"KDB라이프 상품요약서에 해당 내용이 있다면 어떤 상품인지 명시해야 함" (상품명 특정 누락). 또한 재질문 시 KDB라이프 관련 내용이 아예 사라져 응답 일관성 문제 확인.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>두 가지 확인 요청드립니다.
 · 요청 1: 근거 문서에 상품명이 있는 경우 반드시 상품명을 특정해 안내하도록 프롬프트 반영 부탁드립니다. (예: "1) 통풍 진단비(특약)로 대비하는 방법" → "1) 통풍 진단비 특약이 있는 상품: KDB라이프핏건강보험(무) - 통풍진단특약N(무)")
 · 요청 2: 동일 질문 재질문 시 KDB라이프 내용이 사라지는 검색 재현성 이슈 원인 확인 부탁드립니다.</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>프롬프트 + 재현성</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>밸루가 확인</t>
         </is>
       </c>
     </row>
     <row r="11" ht="118" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>FA AI</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>43417</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>응답부족</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>실비 보험 넣을려고 하는데 현재 실비보험 단독으로는 설계가 안되나요?</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>"제공된 자료", "~것으로 안내되어 있습니다", "~있었다고 정리되어 있습니다" 등 내부 피드백용 어투가 고객 노출됨.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>원하시는 답변 톤이나 문장 예시를 함께 전달해주시면 검토에 도움이 될 것 같습니다.</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>[3_답변어투가이드] / [3-1_프롬프트문구초안] 시트로 톤·예시 문장 전달드립니다.
 · 해당 건 Before/After 예시를 가이드에 포함했습니다. (출처 언급 9회 발생)
 · 핵심: 출처 언급 서두(제공된 자료/학습된 내용) 전면 삭제 후 두괄식 결론으로 시작.</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>프롬프트 개선</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>밸루가 반영</t>
         </is>
       </c>
     </row>
     <row r="12" ht="118" customHeight="1">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>FA AI</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="4" t="n">
         <v>43418</v>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>응답실패</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>실비보험 만기가 제일 긴게 어디상품이야?</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>"제공된 자료에는", "확정할 근거가 부족합니다" 등 내부 피드백용 어투. 추가로 정상 답변 뒤에 fallback 문구가 중복 출력됨.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>원하시는 답변 톤이나 문장 예시를 함께 전달해주시면 검토에 도움이 될 것 같습니다.</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>[3_답변어투가이드] / [3-1_프롬프트문구초안] 시트로 톤·예시 문장 전달드립니다. (해당 건 Before/After 포함)
 · 추가 요청: 본문에서 이미 답변(100세 만기)을 제공했음에도 말미에 "현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다" fallback 문구가 중복 출력되고 있습니다. 답변이 생성된 경우 fallback이 함께 붙지 않도록 분기 처리 부탁드립니다. (No.16도 동일 현상)</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>프롬프트 개선</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>밸루가 반영</t>
         </is>
       </c>
     </row>
     <row r="13" ht="118" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>FA AI</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="4" t="n">
         <v>43423</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>응답부족</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>고양이 펫보험 동물등록증 없이 가입가능한 상품있어?</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>"제공된 자료 기준으로는", "~이라고 안내되어 있습니다", "제공된 약관 내용(KB 고양이 펫보험)에는 ~ 확인됩니다" 등 고객이 보는 내용임에도 내부 피드백용 어투 사용.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>원하시는 답변 톤이나 문장 예시를 함께 전달해주시면 검토에 도움이 될 것 같습니다.</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>[3_답변어투가이드] / [3-1_프롬프트문구초안] 시트로 톤·예시 문장 전달드립니다.
 · 해당 건 Before/After 예시를 가이드에 포함했습니다. (출처 언급 10회 발생)</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>프롬프트 개선</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>밸루가 반영</t>
         </is>
       </c>
     </row>
     <row r="14" ht="118" customHeight="1">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>FA AI</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="4" t="n">
         <v>43434</v>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>응답실패</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>드림케어겔</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>일반적인 청결제 제품명. 이런 일반 상식 수준 내용까지 일일이 학습시킬 수 없으므로, 웹검색이나 기본 AI 지식을 활용해 답변할 수 없는지 문의.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>일반상식내용에 대해서 워크플로우 처리하여 웹검색으로 가능한지
 아니면 사용자가 직접 웹검색 버튼누르고 검색하도록 할지 방안 선택 필요</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>[iFA 검토 의견 — 확정 필요]
 · 권고안: 1단계는 "사용자 트리거 방식"(웹검색으로 확인하기 버튼 노출)을 우선 적용 제안드립니다.
@@ -1501,111 +2196,111 @@
 · 확인 요청: 위 2단계 분류 로직(도메인 판별) 구현 가능 여부 및 공수 회신 부탁드립니다.</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>기타(정책)</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>iFA 확정 → 밸루가 회신</t>
         </is>
       </c>
     </row>
     <row r="15" ht="118" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>FA AI</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="4" t="n">
         <v>43473</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>응답부족</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>iFA 퀵 가입설계 메뉴 말하는거야</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>퀵 가입설계 메뉴의 사용법·기능을 안내하지 못함. 「영업 1팀_영업기획팀_퀵가입설계_202500902_00960378.xlsx」 파일은 있으나 메뉴 위치 데이터가 존재하지 않음.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>메뉴 위치·접속 경로에 대한 자료가 현재 학습 대상에 없습니다.
 · iFA에서 퀵 가입설계 화면 사용 매뉴얼(메뉴 경로·기능·출력 방법)을 추가 작성/등록하겠습니다.
 · 등록 후 재검증 요청드립니다. (No.16과 동일 원인)</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>데이터 보강</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>iFA 매뉴얼 등록</t>
         </is>
       </c>
     </row>
     <row r="16" ht="118" customHeight="1">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>FA AI</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="4" t="n">
         <v>43471</v>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>응답부족</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>퀵 가입설계에서 종신과 정기 보험 비교 할수 있어? 출력이 가능하나?</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>퀵 가입설계에서 비교 가능하며 조회 자료 인쇄가 가능하다는 점을 안내하지 못함. 「영업 1팀_영업기획팀_퀵가입설계_202500902_00960378.xlsx」 파일은 있으나 종신/정기 비교 데이터가 존재하지 않음.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>기능 사실관계(비교 가능 / 인쇄 출력 가능)를 담은 매뉴얼을 iFA에서 추가 등록하겠습니다. (No.15와 동일 조치)
 · 추가 요청: 본 건도 본문 답변이 생성되었음에도 말미에 fallback 문구가 중복 출력되고 있습니다. 분기 처리 부탁드립니다. (No.12 동일)</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>데이터 보강 + 프롬프트</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>iFA 매뉴얼 등록 + 밸루가</t>
         </is>
@@ -1617,7 +2312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1647,1153 +2342,1153 @@
       </c>
     </row>
     <row r="3" ht="67.5" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>현황. 출처 언급 어투는 "프롬프트 개선" 분류 4건이 아니라, 답변이 생성된 9건 전부에서 발생 중</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>QA 번호</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>출처 언급 횟수</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>주요 출현 표현</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>밸루가 분류</t>
         </is>
       </c>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>No.10 통풍환자 가입가능 보험</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>19회</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>되어 있습니다(7) · 제공된 자료(2) · 안내되어 있습니다(2) · 자료상 · 자료에 명시 · 자료에 등장</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>(미분류)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>No.3 다이렉트 보험 가입</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>11회</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>자료에 따르면(4) · 제공된 자료(2) · 되어 있습니다(2) · 자료 기준(2)</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>(미분류)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>No.12 실비보험 만기</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>10회</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>제공된 자료(3) · 근거가 부족 · 정리되어 있습니다 · 자료상</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>프롬프트 개선</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>No.13 고양이 펫보험</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>10회</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>되어 있습니다(2) · 자료에는(2) · 확인됩니다 · 안내되어 있습니다</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>프롬프트 개선</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>No.11 실비 단독설계</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>9회</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>되어 있습니다(4) · 제공된 자료(2) · 안내되어 있습니다(2) · 정리되어 있습니다</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>프롬프트 개선</t>
         </is>
       </c>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>No.16 퀵 가입설계 비교</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>7회</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>제공된 자료(2) · 제공 자료 · 자료 기준 · 자료에는</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>(미분류)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>No.4 화상 진단비</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>2회</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>제공된 약관 · 자료에는</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>(미분류)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>No.6 클레임 대응</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>1회</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>제공된 내용의 관점에서는</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>프롬프트 개선</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>No.8 명함 제작</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>1회</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>질의응답 기준으로는</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>데이터확인</t>
         </is>
       </c>
     </row>
     <row r="14" ht="94.5" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>[참고] No.2 · No.14 · No.15는 "학습된 내용" 문구가 있으나 답변 미생성 시의 fallback 안내문이므로 정상입니다. 현행 유지가 맞습니다.</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
     </row>
     <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>원칙 1. 답변은 "고객에게 말하는 문장"이다 — 검색 결과 보고서가 아니다</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>원칙</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>출처 언급 서두를 쓰지 않는다</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>"제공된 자료 기준으로는", "학습한 자료에 따르면", "자료에 따르면", "제공된 약관 내용에는" 등은 문장에서 통째로 삭제하고 바로 본론으로 들어간다.</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>가장 다수 지적 사항</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>전언체(~라고 되어 있습니다)를 단정체(~입니다)로 바꾼다</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>지식 출처가 사내 문서라는 사실은 시스템 내부 사정이므로 문장에 드러내지 않는다.</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>두괄식으로 시작한다</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>"결론부터 말씀드리면, ~" 형태로 첫 문장에 답을 준다. 배경 설명은 그 뒤.</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>모르는 것은 "근거 부족"이 아니라 "확인이 필요한 항목"으로 표현한다</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>"확정할 근거가 부족합니다"(X) → "정확히 안내드리려면 가입하신 상품명 확인이 필요합니다"(O)</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>1-5</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>근거 문서에 상품명·기관명이 있으면 반드시 특정해서 말한다</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>"어떤 자료에 있습니다"로 끝내지 말고 상품명/팀명/연락처까지 명시한다.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>QA No.10 관련</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>1-6</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>없는 내용을 추론해서 단정하지 않는다</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>원문에 없는 제약("임의 제작은 불가")을 만들어내지 않는다. 원문 범위 내에서만 단정한다.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>QA No.8 관련</t>
         </is>
       </c>
     </row>
     <row r="23" ht="27" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>1-7</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>답변이 생성된 경우 fallback 문구를 함께 붙이지 않는다</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>본문 답변이 있는데 말미에 "현재 학습된 내용에는 ~ 어렵습니다"가 중복 출력되지 않도록 분기한다.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>QA No.12, 16 관련</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>1-8</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>학습 내용이 전혀 없을 때의 기존 fallback 문구는 그대로 유지한다</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>"현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다 ~" 안내는 현행 유지가 맞다.</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>유지 요청</t>
         </is>
       </c>
     </row>
     <row r="25" ht="67.5" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>원칙 2. 금지 표현 → 대체 표현 사전 (A: 출처 언급 / B: 전언체 / C: 시스템 한계 노출)</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>금지 표현 (현재 출력)</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>대체 표현 (권장)</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>적용 예 / 출처</t>
         </is>
       </c>
     </row>
     <row r="27" ht="27" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>A-1</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>제공된 자료 기준으로는 ~</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>(삭제 후 바로 본론) ~</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>"제공된 자료 기준으로는 다이렉트 보험은 ~" → "다이렉트 보험은 ~" (No.3, 13, 16)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>A-2</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>제공된 자료에는 / 제공 자료에서는 ~</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>(삭제) ~</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>No.10, 12, 16</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>A-3</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>제공된 내용의 관점에서는 ~</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>(삭제) ~</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>No.6 — 밸루가 빨간색 지적 문구</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>A-4</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>제공된 약관 예시들에서는 / 제공된 약관 내용에는 ~</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>약관에서는 ~ / 약관상 ~</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>No.4, 13</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>A-5</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>학습한 자료에 따르면 ~</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>(삭제) ~</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>"학습한 자료에 따르면 전동킥보드는 ~" → "전동킥보드는 ~"</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>A-6</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>자료에 따르면 ~</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>(삭제) ~</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>No.3에서 4회 반복 출현</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>A-7</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>자료상 ~ / 자료 기준 ~</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>(삭제) ~</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>No.10, 12</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>A-8</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>자료에 명시된 내용 / 자료에 등장한 / 자료에 나온 ~</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>(삭제) ~</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>No.10</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>A-9</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>질의응답 기준으로는 ~</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>(삭제) ~</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>No.8 지적 문구</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>A-10</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>자료에 포함된 예시는 아래와 같습니다</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>대표적으로 아래 상품이 있습니다</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>No.10</t>
         </is>
       </c>
     </row>
     <row r="37" ht="27" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>B-1</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>~것으로 안내되어 있습니다</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>~입니다 / ~할 수 있습니다</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>"단독설계가 가능한 것으로 안내되어 있습니다" → "단독으로 가입하실 수 있습니다" (No.10, 11, 13)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>B-2</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>~라고 정리되어 있습니다</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>~입니다</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>No.11, 12</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>B-3</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>~고 되어 있습니다 / ~로 되어 있습니다</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>~입니다</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>No.10에서 7회, No.11에서 4회 — 가장 빈번한 전언체</t>
         </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>B-4</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>~내용이 확인됩니다 / ~이 확인됩니다</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>~이 있습니다 / ~입니다</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>No.13</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>B-5</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>~라고 안내하고 있습니다</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>~입니다</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>B-6</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>~는 취지입니다 / ~라는 관점입니다</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>~입니다</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>No.6</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>C-1</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>확정할 근거가 부족합니다</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>정확히 안내드리려면 ○○ 확인이 필요합니다</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>No.12 지적 문구</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>C-2</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>학습한 자료만으로는 확인할 수 없습니다</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>가입하신 증권(또는 약관)에서 ○○ 항목을 확인해 주시면 정확히 안내드릴 수 있습니다</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>C-3</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>현재 제공된 정보에 구체적인 안내가 없어 확인이 어렵습니다</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>이 부분은 담당 부서(○○팀)에 확인이 필요한 내용입니다</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>No.16</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>C-4</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>현재 학습된 내용에는 ~ (답변 본문이 있는데도 말미에 덧붙는 경우)</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>(삭제) — 답변을 전혀 생성하지 못한 경우에만 단독 출력</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>No.12, 16 — fallback 중복 출력</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>C-5</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>자료에 직접적인 안내가 없어 확답이 어렵습니다</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>이 기능은 시스템 담당 부서 확인이 필요합니다. ○○로 문의해 주시기 바랍니다</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>No.16</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40.5" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>원칙 3. 답변 구조 템플릿 (기대답변 16건에서 공통 추출)</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>구성 요소</t>
         </is>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>작성 규칙</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>예시 문장</t>
         </is>
       </c>
     </row>
     <row r="50" ht="27" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>공감 한 문장 (사고·질병·손해 문의일 때만)</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>1문장 이내. 형식적 사과가 아닌 상황 공감.</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>"많이 놀라셨겠어요. 팔이 부러질 정도면 통증도 심하고 일상생활도 불편하실 텐데요."</t>
         </is>
       </c>
     </row>
     <row r="51" ht="27" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>두괄식 결론</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>"결론부터 말씀드리면, ~" 으로 시작하고 첫 3줄 안에 답을 준다.</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>"결론부터 말씀드리면, 보험 처리가 가능합니다. 다만 어떤 킥보드를 탔느냐에 따라 차이가 있습니다."</t>
         </is>
       </c>
     </row>
     <row r="52" ht="27" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>근거·구분 (번호 2~4개)</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>조건이 갈리는 지점을 번호로 나눈다. 각 항목 아래 불릿 + 구체 수치.</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>"1. 자가 킥보드를 타다 다친 경우 / 2. 공유 킥보드를 타다 다친 경우"</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>비교표 (선택)</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>선택지가 2개 이상이면 표로 한눈에 정리.</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>"구분 | 신경성형술 등 | 척추 내시경 수술"</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>⚠️ 주의 또는 💡 요약 (택1)</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>리스크가 있으면 ⚠️ 주의, 없으면 💡 한 줄 요약으로 마무리.</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>"💡 암진단비 = 초기 목돈 / 암주요치료비 = 무한 리필 치료비 방패"</t>
         </is>
       </c>
     </row>
     <row r="55" ht="27" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>다음 행동 안내</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>필요 서류·확인처·연락처 등 고객이 바로 할 수 있는 행동을 제시.</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>"서류 준비: 진단서(골절 분류코드 S42, S52 등), 치료비 영수증, 앱 이용 기록 캡처"</t>
         </is>
       </c>
     </row>
     <row r="56" ht="27" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>마무리 권유 (선택)</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>단정 대신 권유형으로 닫는다.</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>"우선은 치료에 전념하시고, 통증이 가라앉으시면 보험사에 연락해 보시길 권해 드립니다."</t>
         </is>
       </c>
     </row>
     <row r="57" ht="27" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>원칙 4. Before / After 실제 예시</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>QA 번호</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>Before (현재 출력)</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>After (권장)</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>변경 포인트</t>
         </is>
       </c>
     </row>
     <row r="59" ht="162" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>No.11
 실비 단독설계</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>### 결론부터 말씀드리면
 - 현재 실손의료보험(실비)은 "단독으로 가입(설계)"이 가능한 상품이 있습니다.
@@ -2801,7 +3496,7 @@
 - 또한 제공된 자료(예: 흥국화재 무 실손의료보험 분석)에서도 "단독설계(특약 없이 실손만 가입 가능)" 형태가 가능한 것으로 안내되어 있습니다.</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>결론부터 말씀드리면, 실손의료보험은 지금도 단독으로 가입하실 수 있습니다.
 1. 단독 가입이 가능한 상품
@@ -2813,7 +3508,7 @@
 나이와 직업, 최근 치료 이력만 알려주시면 가능한 방향으로 안내해 드리겠습니다.</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>· 출처 언급 3회 전부 삭제
 · 상품명은 그대로 살림
@@ -2823,20 +3518,20 @@
       </c>
     </row>
     <row r="60" ht="162" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>No.13
 고양이 펫보험</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>### 결론: 동물등록증(등록번호) 없이도 가입 "가능한 경우"가 있습니다
 - 제공된 자료 기준으로는 동물등록번호가 없어도 '사진 제출' 방식으로 진행되는 케이스가 확인됩니다.
 - 제공된 약관 내용(KB 고양이 펫보험)에는 등록 여부에 따라 제출서류가 달라지는 기준이 확인됩니다.</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>결론부터 말씀드리면, 동물등록증이 없어도 가입하실 수 있는 경우가 있습니다.
 1. 등록번호 대신 사진으로 대체됩니다
@@ -2847,7 +3542,7 @@
 고양이 나이와 중성화 여부, 병력 유무를 알려주시면 가입 가능한 상품으로 좁혀 안내해 드리겠습니다.</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>· "제공된 자료 기준으로는" 삭제
 · "~확인됩니다" → "~합니다"
@@ -2856,20 +3551,20 @@
       </c>
     </row>
     <row r="61" ht="94.5" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>No.6
 클레임 대응</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>### 무조건 "죄송합니다"라고 사과해야 하나요?
 - 제공된 내용의 관점에서는 무조건적인 사과("죄송합니다" 반복)는 권하지 않습니다.
 - 이유는, 형식적인 사과가 오히려 무성의하게 느껴질 수 있고, 이후에 효과적인 질문을 통해 구체 정보를 얻는 흐름을 막을 수 있다는 취지입니다.</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>무조건적인 사과를 반복하는 것은 권해 드리지 않습니다.
 형식적인 사과는 오히려 무성의하게 느껴질 수 있고, 고객에게서 구체적인 정보를 얻어낼 기회를 막기 때문입니다.
@@ -2877,7 +3572,7 @@
 "정말 감사합니다. 바쁘신 와중에도 저희 잘못을 지적해 주신 데 대한 감사의 표시입니다. 말씀하신 사항을 반드시 적용하겠습니다."</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>· "제공된 내용의 관점에서는" 삭제 (밸루가 빨간색 지적 문구)
 · "~라는 취지입니다" → "~때문입니다"</t>
@@ -2885,13 +3580,13 @@
       </c>
     </row>
     <row r="62" ht="175.5" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>No.3
 다이렉트 보험</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>- 제공된 자료 기준으로 다이렉트 보험은 보험사가 고객에게 직접 판매하는 방식이라서, 원칙적으로는 고객 본인이 직접 가입하는 구조입니다.
   (자료에 따르면, 일부 보험비교사이트는 대리점이 운영하며 …)
@@ -2899,7 +3594,7 @@
 - 자료에 따르면 보험사별로 보험료 차이가 있을 수 있어 …</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>다이렉트 보험은 보험사가 고객님께 직접 판매하는 방식이라, 원칙적으로는 고객님이 직접 가입하시는 구조입니다.
 다만 담당 설계사가 보내드린 가입 링크를 통해서도 다이렉트 가입이 가능합니다.
@@ -2909,7 +3604,7 @@
 ⚠️ 다이렉트가 항상 저렴한 것은 아닙니다. 설계사 수당이 빠져 대체로 저렴하지만, 손해율이 높은 일부 보험사의 다이렉트 상품은 비교사이트보다 비쌀 수도 있습니다.</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>· 출처 언급 11회 전부 삭제
 · 누락됐던 "설계사 링크로 가입 가능" 사실 추가 (기대 답변 반영)
@@ -2918,13 +3613,13 @@
       </c>
     </row>
     <row r="63" ht="216" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>No.10
 통풍환자 보험</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>- 제공된 자료 기준으로는 통풍 관련 보장을 담은 상품/특약이 존재하며 …
 ### 1) 통풍 진단비(특약)로 대비하는 방법
@@ -2933,7 +3628,7 @@
 - 장점으로 자료에 명시된 내용: …</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>통풍이 있으셔도 가입하실 수 있는 보험이 있습니다.
 1. 통풍 진단비 특약이 있는 상품
@@ -2946,7 +3641,7 @@
 최근 진단·입원·수술 시점과 현재 복용 중인 약이 있으신지 알려주시면 가입 가능한 상품으로 좁혀 안내해 드리겠습니다.</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>· 출처 언급 19회 전부 삭제 (최다 발생 건)
 · 밸루가 지적 반영: "통풍 진단비로 대비하는 방법" → 상품명 특정("KDB라이프핏건강보험(무)")
@@ -2955,13 +3650,13 @@
       </c>
     </row>
     <row r="64" ht="121.5" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>No.12
 실비 만기</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>- 제공된 자료에는 특정 보험사/상품을 비교해서 "어디 상품이 만기가 제일 길다"를 단정할 수 있는 전체 상품 비교표가 없습니다.
 - "어느 회사/어느 상품이 100세 만기인지"를 특정해 드리기에는, 현재 제공된 자료만으로는 상품명/보험사별 현행 판매 상품을 확정할 근거가 부족합니다.
@@ -2969,7 +3664,7 @@
 현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다. 다른 주제 또는 조금 더 구체적으로 질문해 주시기 바랍니다. …</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>실비보험 만기는 현재 100세 만기가 가장 깁니다.
 과거에는 80세 만기가 일반적이었으나 보장기간이 확대되면서 지금은 100세 만기 구성까지 나와 있습니다.
@@ -2979,7 +3674,7 @@
 3. 현재 가입 중이신 실손이 있으시면 보험사·상품명·가입년도</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>· 출처 언급 10회 삭제
 · "확정할 근거가 부족합니다"(시스템 한계) → "알려주시면 좁혀 드리겠습니다"(고객 행동)
@@ -3002,13 +3697,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3025,24 +3720,24 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>적용: FA AI / Orca AI 공통 · 근거: [3_답변어투가이드] 원칙 1~2 · 문구는 iFA 초안이며 밸루가측 검토 후 조정 가능합니다</t>
+          <t>적용: FA AI / Orca AI 공통 · 「AI 답변 품질 개선 종합 보고서」의 프롬프트 지침(전달 구조)과 QA검증요청 9건 실측(출처 언급·전언체)을 하나로 통합한 단일본입니다</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="700" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="1150" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>프롬프트 본문
 (복사용)</t>
@@ -3050,51 +3745,103 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>[답변 어투 규칙]
-1. 당신은 고객에게 직접 말하는 보험 상담사입니다. 검색 결과를 요약해 보고하는 것이 아닙니다.
-   답변은 사내 문서를 정리한 보고서가 아니라, 상담사가 고객에게 건네는 말이어야 합니다.
-2. 지식의 출처가 내부 문서라는 사실을 문장에 드러내지 마십시오.
-   아래 표현은 어떤 경우에도 사용하지 않습니다. 해당 구절은 삭제하고 바로 본론으로 들어갑니다.
-   - "제공된 자료", "제공된 내용", "제공된 약관", "제공 자료"
-   - "학습한 자료", "학습된 내용", "학습 자료"
-   - "자료에 따르면", "자료상", "자료 기준으로는", "자료에는", "자료에 명시된", "자료에 등장한"
-   - "질의응답 기준으로는"
-3. 전언체를 쓰지 말고 단정체로 서술하십시오.
-   - "~라고 되어 있습니다", "~것으로 안내되어 있습니다", "~라고 정리되어 있습니다",
-     "~이 확인됩니다", "~라는 취지입니다"
-   → "~입니다", "~할 수 있습니다", "~때문입니다"
-4. 첫 문장은 결론입니다. "결론부터 말씀드리면, ~" 형태로 시작하고 3줄 안에 답을 제시하십시오.
-   배경 설명과 조건 분기는 결론 뒤에 둡니다.
-5. 확인이 필요한 경우, 시스템의 한계가 아니라 고객이 할 행동으로 표현하십시오.
-   - (X) "확정할 근거가 부족합니다"
-   - (X) "학습한 자료만으로는 확인할 수 없습니다"
-   - (O) "정확히 안내드리려면 가입하신 상품명 확인이 필요합니다"
-   - (O) "증권의 담보명 부분을 알려주시면 정확히 안내드리겠습니다"
-6. 근거 문서에 상품명·회사명·팀명·연락처 등 고유명사가 있으면 반드시 그대로 특정해 안내하십시오.
-   - (X) "통풍 진단비 특약이 있는 상품이 존재합니다"
-   - (O) "KDB라이프핏건강보험(무)의 통풍진단특약N(무)이 있습니다"
-7. 근거 문서에 없는 제약·금지·예외를 추론해서 단정하지 마십시오.
-   문서에 "개별 제작이 가능하다"고만 되어 있으면 "임의 제작은 불가"라고 확장하지 않습니다.
-8. 본문 답변을 생성한 경우, 말미에 "현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다 …"
-   안내문을 덧붙이지 마십시오. 이 안내문은 답변을 전혀 생성하지 못한 경우에만 단독으로 출력합니다.
-9. 마크다운 헤딩(###)과 볼드(**)를 과도하게 사용하지 말고,
-   번호(1. 2. 3.)와 불릿(•) 중심의 상담 문장으로 작성하십시오.
-10. 질문에 사고 경위가 명시된 경우, 그 경위와 무관한 담보를 함께 안내하지 마십시오.
-    (예: "요리하다 화상" 질문에 교통상해 화상진단비를 병기하지 않습니다.)
-11. 답변 마지막은 고객이 바로 할 수 있는 행동으로 닫으십시오.
-    필요 서류, 확인처, 문의할 부서·연락처, 또는 추가로 알려주셔야 할 정보를 제시합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+          <t>## 답변 방식
+### 핵심 원칙
+정보를 많이 제공하는 것보다, 고객이 읽고 나서 "그래서 나는 어떻게 해야 하는가"를 바로 알 수 있게
+전달하는 것이 목표입니다. 회사 AI의 문제는 정보 부족이 아니라, 가진 정보를 전달하지 못하는 구조입니다.
+### 답변 구조
+1. 결론을 첫 문장에 제시합니다.
+   예) "네, 가능합니다." / "받을 수 있습니다." / "종류에 따라 다릅니다."
+2. 이유·조건은 결론 이후에 간결하게 설명합니다.
+3. 조건 비교는 표 1개로 시각화합니다.
+4. 숫자 시뮬레이션 또는 비유 1개를 활용합니다.
+5. 마지막에 "상황별 전략 요약" 1줄을 넣습니다.
+   예) "재산이 10억 초과라면 증여, 이하라면 상속이 유리합니다."
+6. 소제목 2개 이하, 불릿 3개 이하, 모바일 한 화면 완결을 목표로 합니다.
+### 금지 표현 — 출처 언급
+지식의 출처가 내부 문서라는 사실을 문장에 드러내지 마십시오.
+아래 표현은 구절째 삭제하고 바로 본론으로 들어갑니다.
+- "학습한 자료에 따르면 / 에는 / 상", "학습된 내용"
+- "제공된 자료", "제공된 내용", "제공된 약관", "제공 자료"
+- "자료에 따르면", "자료상", "자료 기준으로는", "자료에는", "자료에 명시된", "자료에 등장한"
+- "질의응답 기준으로는"
+### 금지 표현 — 전언체
+아래 어미는 단정체로 바꿉니다.
+- "~라고 되어 있습니다", "~것으로 안내되어 있습니다", "~라고 정리되어 있습니다",
+  "~이 확인됩니다", "~라는 취지입니다"
+→ "~입니다", "~할 수 있습니다", "~때문입니다"
+### 금지 표현 — 기타
+- 약관·법조문 직접 인용 (고객 언어로 요약)
+- 같은 내용 반복 서술
+- "정리하면" / "종합하면" 섹션 별도 추가
+- 면책 문구 본문 중간 삽입
+- "100% 가능합니다" 등 단정적 표현
+### 확인이 필요한 경우
+시스템의 한계가 아니라, 고객이 할 행동으로 표현합니다.
+- (X) "확정할 근거가 부족합니다"
+- (X) "학습한 자료만으로는 확인할 수 없습니다"
+- (O) "정확히 안내드리려면 가입하신 상품명 확인이 필요합니다"
+### 근거 문서 활용
+- 근거 문서에 상품명·회사명·팀명·연락처 등 고유명사가 있으면 반드시 그대로 특정해 안내합니다.
+  (X) "통풍 진단비 특약이 있는 상품이 존재합니다"
+  (O) "KDB라이프핏건강보험(무)의 통풍진단특약N(무)이 있습니다"
+- 근거 문서에 없는 제약·금지·예외를 추론해서 단정하지 마십시오.
+- 질문에 사고 경위가 명시된 경우, 그 경위와 무관한 담보를 함께 안내하지 마십시오.
+  (예: "요리하다 화상" 질문에 교통상해 화상진단비를 병기하지 않습니다.)
+### 답변 미생성 시 안내문 처리
+본문 답변을 생성한 경우, 말미에 "현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다 …"
+안내문을 덧붙이지 마십시오. 이 안내문은 답변을 전혀 생성하지 못한 경우에만 단독으로 출력합니다.
+### 질문 유형별 전달 방식
+사고·부상 질문:
+  첫 줄 공감 → 청구 가능한 모든 루트 안내 → 지금 당장 해야 할 행동 요령 → 마지막 위로 문구
+  예) 부상: "빠른 쾌유를 바랍니다." / 사고 후 불안: "많이 놀라셨겠습니다."
+비교·선택 질문 (증여 vs 상속, 전세 vs 월세 등):
+  표로 나란히 비교 → 마지막에 상황별 전략 요약 한 줄
+'있나요?' 질문:
+  있다는 사실 + 활용 방법 + 주의사항을 세트로 답합니다.
+'왜 필요한가?' 질문:
+  기능 나열이 아니라 맥락·트렌드 변화로 먼저 설명합니다.
+보험 종류에 따라 답이 달라지는 질문:
+  종류별로 나눠서 표로 제시합니다.
+법령·정의 질문:
+  정의 → 왜 중요한지 → 주요 예외 순서로 답합니다.
+'쉽게 설명해줘' 질문:
+  숫자 시뮬레이션 또는 비유 1개를 반드시 포함합니다.
+고객이 개인 정보를 제공한 경우 (처음 탔다, 약 2년 복용 등):
+  그 정보를 즉시 답변에 반영합니다. 일반 답변이 아닌 맞춤 답변을 제공합니다.
+### 마무리
+전문가 상담 권고 등 면책 문구는 마지막 1줄에만 넣습니다.
+형식: &gt; 정확한 판단은 [전문가] 상담을 권장드립니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="100" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>통합 출처</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>· 「답변 구조」 「금지 표현 — 기타」 「질문 유형별 전달 방식」 「마무리」
+   → AI 답변 품질 개선 종합 보고서(19개 케이스 분석)의 프롬프트 지침 원안
+· 「금지 표현 — 출처 언급」 「금지 표현 — 전언체」 「확인이 필요한 경우」
+   「근거 문서 활용」 「답변 미생성 시 안내문 처리」
+   → 본 QA검증요청 9건 실측 기반 iFA 추가분 ([3_답변어투가이드] 참조)
+※ 보고서의 금지 표현 목록은 "학습한 자료에" 계열 중심이었으나, QA검증 답변에서는 "제공된 자료" 계열이 더 빈번해 함께 포함했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>적용 후 기대 효과</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>· 출처 언급 어투 9건 → 0건
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>· 출처 언급 어투 9건 → 0건 (보고서 기준 13/19 케이스)
+· 결론 후배치 해소 (보고서 기준 13/19 케이스)
 · fallback 중복 출력 2건(No.12, 16) 해소
 · 상품명 미특정 1건(No.10) 해소
 · 무관 담보 병기 1건(No.4) 재발 방지
@@ -3102,13 +3849,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>유지 요청 사항</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>학습된 내용을 전혀 찾지 못한 경우의 기존 fallback 안내문은 현행 그대로 유지해 주시기 바랍니다.
 ("현재 학습된 내용에는 원하시는 답변을 제공하기 어렵습니다. 다른 주제 또는 조금 더 구체적으로 …")
@@ -3125,7 +3872,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3155,22 +3902,22 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>검수 항목</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>판정 기준</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>자동 검출 키워드</t>
         </is>
@@ -3182,17 +3929,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>출처 언급 문구가 없는가</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>아래 키워드가 답변에 1회도 등장하지 않으면 통과</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>제공된 자료 / 제공된 내용 / 제공된 약관 / 제공 자료 / 학습한 자료 / 학습된 내용 / 자료에 따르면 / 자료상 / 자료 기준 / 자료에는 / 자료에 명시 / 질의응답 기준</t>
         </is>
@@ -3204,17 +3951,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>전언체가 아닌 단정체인가</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>아래 어미가 등장하지 않으면 통과</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>되어 있습니다 / 안내되어 있습니다 / 정리되어 있습니다 / 확인됩니다 / 라는 취지입니다</t>
         </is>
@@ -3226,17 +3973,17 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>첫 3줄 안에 결론이 제시되는가</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>첫 문단에 "가능합니다 / 어렵습니다 / ~입니다" 형태의 답이 있으면 통과</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>결론부터 말씀드리면</t>
         </is>
@@ -3248,17 +3995,17 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>시스템 한계를 노출하지 않는가</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>고객 행동 요청 형태로 표현됐으면 통과</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>근거가 부족 / 확인할 수 없습니다 / 확답이 어렵습니다 / 확정할 수 없습니다</t>
         </is>
@@ -3270,17 +4017,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>고유명사가 특정되어 있는가</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>근거 문서에 상품명·팀명이 있으면 답변에도 그대로 등장해야 통과</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>(수동 확인) 상품 / 특약 / 팀 언급 시 명칭 유무</t>
         </is>
@@ -3292,17 +4039,17 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>fallback이 중복 출력되지 않는가</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>본문 답변이 있으면 말미 안내문이 없어야 통과</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>현재 학습된 내용에는 (본문 길이 200자 초과 시 동시 출현 여부)</t>
         </is>
@@ -3314,17 +4061,17 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>근거 없는 단정이 없는가</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>원문에 없는 금지·제약 표현을 만들지 않았으면 통과</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>(수동 확인) 불가 / 안 됩니다 / 해서는 안 / 필수입니다</t>
         </is>
@@ -3336,17 +4083,17 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>무관한 담보를 병기하지 않았는가</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>질문의 사고 경위와 다른 담보가 안내되지 않으면 통과</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>(수동 확인)</t>
         </is>
@@ -3358,17 +4105,17 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>마무리에 행동 안내가 있는가</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>필요 서류·확인처·추가 문의 정보 중 하나가 제시되면 통과</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>(수동 확인)</t>
         </is>
@@ -3391,7 +4138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3414,37 +4161,37 @@
       </c>
     </row>
     <row r="2" ht="200" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>사용자 질문</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>현재 AI 답변</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>기대 답변 (톤 레퍼런스)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="200" customHeight="1">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>사망보험금 1억 받으면 상속세 내야 하나요? 보험금도 상속 재산에 포함되나요?</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>핵심
 • 사망보험금 1억을 받았다고 해서 무조건 상속세가 나오는 것은 아닙니다.
@@ -3453,7 +4200,7 @@
 실질적으로 돌아가신 분이 보험료를 부담한 경우가 핵심입니다.</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>결론부터 말씀드리면, 사망보험금 1억 원은 '상속재산'에 포함되는 것이 맞지만, 대부분의 경우 상속세는 단 1원도 내지 않습니다.
 1. 보험금도 상속재산에 포함되나요?
@@ -3471,15 +4218,15 @@
       </c>
     </row>
     <row r="4" ht="200" customHeight="1">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>전동킥보드를 타다 팔이 골절됐는데, 보험 처리가 되나요?</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>전동킥보드 사고는 일상생활배상책임보험으로는 보상되지 않을 가능성이 큽니다.
 학습한 자료에 따르면 전동킥보드는 도로교통법상 차량으로 분류되어, 전동킥보드 운행 중 발생한 사고는 일상생활배상책임보험의 차량 사용 관련 면책에 해당할 수 있습니다.
@@ -3490,7 +4237,7 @@
 고객님이 가입하신 보험에 전동킥보드·개인형 이동장치(PM) 관련 담보가 있는지는 학습한 자료만으로는 확인할 수 없습니다.</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>많이 놀라셨겠어요. 팔이 부러질 정도면 통증도 심하고 당장 일상생활도 많이 불편하실 텐데, 치료는 잘 받으셨는지 모르겠습니다.
 결론부터 말씀드리면 보험 처리가 가능합니다. 다만, 어떤 킥보드를 탔느냐에 따라 아주 중요한 차이가 있습니다.
@@ -3509,15 +4256,15 @@
       </c>
     </row>
     <row r="5" ht="200" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>금리가 오르면 전세가 유리할까요, 월세가 유리할까요?</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>금리가 오르면 보통 전세보다 월세가 더 현실적인 선택지로 떠오르는 경향이 있습니다.
 이유는 학습한 자료상 크게 두 가지입니다.
@@ -3534,7 +4281,7 @@
 결국 "금리가 오르면 대체로 월세 쪽이 상대적으로 유리해질 수 있지만, 최종 판단은 전세대출 이자와 전월세 전환율을 직접 비교해야 한다"고 보시면 됩니다.</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>결론부터 말씀드리면, 금리가 오를 때는 세입자 입장에서 월세(또는 반전세)가 더 유리해지는 경우가 많습니다.
 1. 금리 상승기에 월세가 유리한 이유 — 숫자로 비교
@@ -3552,15 +4299,15 @@
       </c>
     </row>
     <row r="6" ht="200" customHeight="1">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>같은 나이라도 사람마다 보험 설계가 달라지는 거야?</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>네, 같은 나이라도 보험 설계는 사람마다 달라질 수 있습니다.
 학습한 자료에 따르면 보험 설계는 단순히 나이만으로 정해지지 않고, 여러 조건을 함께 봐야 합니다.
@@ -3576,7 +4323,7 @@
 즉, 보험은 나이가 같다고 같은 설계가 정답인 것이 아니라, 내 상황에 맞게 필요한 보장은 충분히 넣고 불필요한 보장은 줄이는 방식이 더 중요합니다.</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">네, 백 퍼센트 다 달라집니다. 심지어 나이, 성별, 직업이 똑같아도 최종 보험 설계는 완전히 다르게 나올 수 있어요.
 달라지는 핵심 이유 4가지:
@@ -3599,15 +4346,15 @@
       </c>
     </row>
     <row r="7" ht="200" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>허리디스크 시술 받으려는데 내시경 시술이랑 수술이랑 보험 보장 금액이 다른가요?</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>네, 다를 수 있습니다.
 학습한 자료에 따르면 수술비 특약은 가입하신 약관 구조가 1~5종인지, 1~7종인지에 따라 내시경 시술과 일반 수술의 보장금액 차이가 달라질 수 있습니다.
@@ -3620,7 +4367,7 @@
 • 다만 허리디스크의 실제 시술명이 어떤 코드와 항목으로 잡히는지는 학습한 자료만으로는 확인할 수 없습니다.</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>네, 다를 수 있습니다.
 1. 실손보험(실비)에서의 차이 — 입원이냐 통원이냐가 핵심
@@ -3642,15 +4389,15 @@
       </c>
     </row>
     <row r="8" ht="200" customHeight="1">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>변액보험 펀드 종류가 너무 많은데, 뭘 골라야 하는 거야?</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>변액보험 펀드는 많아 보여도, 기준은 크게 어렵지 않습니다. 내 투자 성향에 맞는 펀드를 고르는 것이 가장 중요합니다.
 기본적으로는 이렇게 보시면 됩니다.
@@ -3668,7 +4415,7 @@
 • 단기 수익만 보고 접근하기보다 장기적인 유지와 관리가 중요합니다.</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>변액보험 펀드를 고를 때는 "단품 메뉴"를 고르는 게 아니라, 내 성향에 맞는 "뷔페 접시(포트폴리오)"를 구성한다고 생각하시면 됩니다.
 1. 딱 3가지만 기억하세요 (펀드의 큰 줄기)
@@ -3692,15 +4439,15 @@
       </c>
     </row>
     <row r="9" ht="200" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>1세대 1주택자의 장기보유특별공제에서 2년 거주 요건을 채우지 못하면 어떤 공제율이 적용되는가?</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>1세대 1주택자라도 2년 이상 거주 요건을 채우지 못하면, 보유기간 연 4% + 거주기간 연 4%를 합산하는 방식의 장기보유특별공제는 적용되지 않습니다.
 이 경우에는 3년째부터 매년 2%씩 공제되는 공제율이 적용됩니다.
@@ -3710,7 +4457,7 @@
 즉, 2년 거주 요건을 못 채우시면 장기보유특별공제율이 크게 낮아질 수 있습니다.</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>1세대 1주택자가 2년 거주 요건을 채우지 못하면, 최대 80%까지 받을 수 있는 공제율(표 2) 대신 일반 다주택자와 동일한 낮은 공제율(표 1)이 적용됩니다.
 1. 2년 거주 미충족 시 적용되는 공제율
@@ -3725,16 +4472,16 @@
       </c>
     </row>
     <row r="10" ht="200" customHeight="1">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">노후 준비 하나도 못 했는데 지금 시작해도 안 늦을까?
 </t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>전혀 늦지 않았습니다.
 학습한 자료에 따르면, 노후 준비는 "늦었다"는 생각이 들 때 시작해도 결코 늦지 않다고 되어 있습니다.
@@ -3752,7 +4499,7 @@
 오히려 가장 아쉬운 선택은 늦게 시작하는 것이 아니라, 걱정만 하면서 계속 미루는 것입니다.</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>결론부터 말씀드리면, 절대 늦지 않았습니다.
 지금 노후 준비가 안 됐다고 느끼시는 것은 "어디서부터 손을 대야 할지 몰라서" 오는 막연한 두려움 때문일 확률이 높습니다.
@@ -3769,15 +4516,15 @@
       </c>
     </row>
     <row r="11" ht="200" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>무배당 KB스타재해사망보험 1년 만기 때 사고가 없었으면 그동안 낸 보험료에서 배당금을 받을 수 있나요?</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>학습한 자료에 따르면, 무배당 상품은 배당을 하지 않습니다.
 따라서 1년 만기까지 사고가 없었다고 해서, 그동안 납입한 보험료에서 배당금을 받는 것은 아닙니다.
@@ -3785,7 +4532,7 @@
 다만, 문의하신 '무배당 KB스타재해사망보험' 자체의 만기환급금이나 해약환급금 여부는 현재 학습된 자료에서 직접 확인되지 않습니다. 그래서 배당금은 없다는 점까지만 확실하게 말씀드릴 수 있습니다.</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>결론부터 말씀드리면, 사고가 없었더라도 배당금은 단 1원도 받을 수 없습니다.
 1. '무배당' 상품이기 때문입니다
@@ -3800,15 +4547,15 @@
       </c>
     </row>
     <row r="12" ht="200" customHeight="1">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>암주요치료비 왜 필요해?</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">암주요치료비는 암 진단 자체보다, 실제 치료가 시작됐을 때를 대비하는 보장이라서 필요할 수 있습니다.
 학습한 자료에는 암주요치료비가 보통 아래 치료를 받았을 때 지급되는 형태로 되어 있습니다.
@@ -3829,7 +4576,7 @@
 </t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>최근 보험 시장에서 가장 핫한 담보가 바로 '암주요치료비' 특약입니다.
 결론부터 말씀드리면, 요즘 암 치료 트렌드가 '입원해서 수술하는 시대'에서 '통원하며 비싼 표적항암치료를 받는 시대'로 바뀌었기 때문입니다.
@@ -3849,15 +4596,15 @@
       </c>
     </row>
     <row r="13" ht="200" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>간염 진단비 나오는 보험이 있나요?</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>네, 있습니다.
 학습한 자료에는 간염(B형, C형) 진단비가 포함된 보험이 확인됩니다.
@@ -3870,7 +4617,7 @@
 다만 정확한 보장 여부는 상품마다 다를 수 있고, 현재 확인되는 것은 B형·C형 간염 기준입니다. 간염 전체가 아니라 B형과 C형에 한해 진단비가 있는 상품이 확인됩니다.</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>네, 당연히 있습니다. 다만 '간염 보험'이라는 이름의 상품이 아니라, 종합건강보험 안에 특약 형태로 포함되어 있습니다.
 간염은 만성으로 진행되면 간경화나 간암으로 발전할 확률이 높기 때문에 보험사에서도 중요하게 다루는 항목입니다.
@@ -3891,15 +4638,15 @@
       </c>
     </row>
     <row r="14" ht="200" customHeight="1">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>아파트 안에 골프연습장에서 넘어졌는데 보험금 받을 수 있어?</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>네, 받을 가능성이 있습니다.
 아파트 내 골프연습장에서 넘어진 사고는 아파트 측이 가입한 보험에 구내치료비 특약이 있으면 보험금 지급이 가능할 수 있습니다.
@@ -3914,7 +4661,7 @@
 • 다만 특약 가입 여부와 사고 발생 사실 확인이 중요합니다.</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>아파트 단지 내 골프연습장에서 넘어지신 경우, 두 가지 루트를 통해 보험금을 받을 수 있습니다.
 1. 내가 가입한 개인 보험 청구
@@ -3933,15 +4680,15 @@
       </c>
     </row>
     <row r="15" ht="200" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>소득세법상 '거주자'의 정의는 무엇인가요?</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>소득세법상 거주자는 국내에 주소를 두거나 183일 이상의 거소를 둔 개인을 말합니다.
 추가로,
@@ -3950,7 +4697,7 @@
 • 국적이나 외국 영주권 보유 여부와는 직접 관련이 없고, 거주기간, 직업, 국내의 가족·자산 유무 등 생활관계를 기준으로 구분합니다.</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>대한민국 소득세법(제1조의2)상 '거주자'의 법적 정의는 다음과 같습니다.
 "국내에 주소를 두거나 183일 이상의 거소(居所)를 둔 개인"
@@ -3971,15 +4718,15 @@
       </c>
     </row>
     <row r="16" ht="200" customHeight="1">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>운전자보험 특약 설명해줘</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>운전자보험의 특약은 기본계약에 추가해서 필요한 보장을 넓히는 항목입니다.
 많이 확인하시는 특약:
@@ -4009,7 +4756,7 @@
 특약마다 가입 조건, 보장 한도, 중복가입 가능 여부, 자기부담금, 자가용·영업용 구분이 다릅니다.</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">운전자보험은 자동차보험(의무 보험)이 채워주지 못하는 '형사적·행정적 책임'을 보장받기 위해 가입하는 보험입니다. 내가 운전하다가 남을 크게 다치게 하거나 사망하게 했을 때 구속되거나 벌금 폭탄을 맞지 않도록 방어막을 치는 특약들로 구성되어 있습니다.
 핵심 3대 특약 + 필수 특약 1가지:
@@ -4037,15 +4784,15 @@
       </c>
     </row>
     <row r="17" ht="200" customHeight="1">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>메디코드는 어떤 서비스인가요?</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>메디코드는 건강검진 데이터와 유전자 데이터를 바탕으로 AI가 미래 질병 위험을 분석하고, 그 결과에 맞춰 꼭 필요한 보장을 설계해드리는 초개인화 보험설계 서비스입니다.
 기존의 일반 보험설계가 통계나 평균적인 기준을 중심으로 보장을 구성하는 방식이라면, 메디코드는 고객님 고유의 데이터를 기반으로 위험도를 분석해 맞춤형 보장을 제안하는 점이 다릅니다.
@@ -4058,7 +4805,7 @@
 이용을 위해서는 본인인증 기반 회원가입이 필요하며, Ai Link에서 메디코드 관련 메뉴나 키워드를 통해 접속하실 수 있습니다.</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>메디코드(MCID, MediCode-based Insurance Design)는 인슈어테크 기업 iFA가 개발한 국내 최초의 '건강검진 및 유전자 데이터 기반 초개인화 보험설계 플랫폼'입니다.
 기존의 보험 설계가 나이·성별 같은 통계적 평균에 의존했다면, 메디코드는 개인의 고유한 건강 리스크를 과학적으로 분석하여 딱 맞는 보험을 제안하는 혁신적인 서비스입니다.
@@ -4077,15 +4824,15 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>어제 길거리 공유 킥보드 타다가 넘어져서 팔이 부러졌는데요. 내가 든 실비 보험에서 병원비 받을 수 있나요? 킥보드는 처음 타본 거예요</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>실비보험에서 병원비를 받을 수 있는지는 보상 제외 조건이 있는지가 가장 중요합니다.
 • 상해를 보장하는 보험은 이륜차 부담보 특약이 있는 경우가 많고, 이 특약이 있으면 이륜자동차를 소유·사용·관리하는 동안 발생한 상해는 보상하지 않을 수 있습니다.
@@ -4094,7 +4841,7 @@
 실제로 어떻게 처리되는지에 대한 확정 기준은 고객님 보험의 약관 확인이 꼭 필요합니다.</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>아이구, 킥보드를 처음 타보셨는데 팔까지 부러지셨다니 정말 많이 놀라시고 아프셨겠습니다.
 결론부터 말씀드리면, 내가 가입한 실비 보험에서 병원비를 정상적으로 돌려받으실 수 있습니다.
@@ -4117,7 +4864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4148,27 +4895,27 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>사용자 질문</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>결과</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>질의 채널 (Cloud / Link)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>기준 원본 문서명</t>
         </is>
@@ -4205,7 +4952,7 @@
       <c r="A5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>사망보험금 1억 받으면 상속세 내야 하나요? 보험금도 상속 재산에 포함되나요?</t>
         </is>
@@ -4215,14 +4962,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>전동킥보드를 타다 팔이 골절됐는데, 보험 처리가 되나요?</t>
         </is>
@@ -4232,14 +4979,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>금리가 오르면 전세가 유리할까요, 월세가 유리할까요?</t>
         </is>
@@ -4249,14 +4996,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>같은 나이라도 사람마다 보험 설계가 달라지는 거야?</t>
         </is>
@@ -4266,14 +5013,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>허리디스크 시술 받으려는데 내시경 시술이랑 수술이랑 보험 보장 금액이 다른가요?</t>
         </is>
@@ -4283,14 +5030,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>변액보험 펀드 종류가 너무 많은데, 뭘 골라야 하는 거야?</t>
         </is>
@@ -4300,14 +5047,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>1세대 1주택자의 장기보유특별공제에서 2년 거주 요건을 채우지 못하면 어떤 공제율이 적용되는가?</t>
         </is>
@@ -4317,14 +5064,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">노후 준비 하나도 못 했는데 지금 시작해도 안 늦을까?
 </t>
@@ -4335,14 +5082,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>무배당 KB스타재해사망보험 1년 만기 때 사고가 없었으면 그동안 낸 보험료에서 배당금을 받을 수 있나요?</t>
         </is>
@@ -4352,14 +5099,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>암주요치료비 왜 필요해?</t>
         </is>
@@ -4369,14 +5116,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>간염 진단비 나오는 보험이 있나요?</t>
         </is>
@@ -4386,14 +5133,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>아파트 안에 골프연습장에서 넘어졌는데 보험금 받을 수 있어?</t>
         </is>
@@ -4403,14 +5150,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>소득세법상 '거주자'의 정의는 무엇인가요?</t>
         </is>
@@ -4420,14 +5167,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>운전자보험 특약 설명해줘</t>
         </is>
@@ -4437,14 +5184,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>메디코드는 어떤 서비스인가요?</t>
         </is>
@@ -4454,14 +5201,14 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>어제 길거리 공유 킥보드 타다가 넘어져서 팔이 부러졌는데요. 내가 든 실비 보험에서 병원비 받을 수 있나요? 킥보드는 처음 타본 거예요</t>
         </is>
@@ -4471,8 +5218,8 @@
           <t>개선필요</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
